--- a/salidas/empresas/IBM.xlsx
+++ b/salidas/empresas/IBM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EPS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="EPS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Info" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -435,58 +447,58 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>precio_ajustado</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>precio_cierre</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>volumen</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pe</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>acciones_circulacion</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>market_cap</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rotacion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>41.10724258422852</v>
+        <v>41.10723495483398</v>
       </c>
       <c r="C2" t="n">
         <v>77.72466278076172</v>
@@ -501,11 +513,11 @@
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>40.67316818237305</v>
+        <v>40.67315673828125</v>
       </c>
       <c r="C3" t="n">
         <v>76.71128082275391</v>
@@ -520,11 +532,11 @@
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>41.80351257324219</v>
+        <v>41.80353927612305</v>
       </c>
       <c r="C4" t="n">
         <v>78.84320831298828</v>
@@ -539,11 +551,11 @@
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>41.73763275146484</v>
+        <v>41.73764038085938</v>
       </c>
       <c r="C5" t="n">
         <v>78.71892547607422</v>
@@ -558,11 +570,11 @@
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>40.64724731445312</v>
+        <v>40.6472282409668</v>
       </c>
       <c r="C6" t="n">
         <v>76.38623046875</v>
@@ -577,11 +589,11 @@
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>39.08035659790039</v>
+        <v>39.08037185668945</v>
       </c>
       <c r="C7" t="n">
         <v>73.44168090820312</v>
@@ -596,11 +608,11 @@
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>39.38051223754883</v>
+        <v>39.38050842285156</v>
       </c>
       <c r="C8" t="n">
         <v>74.0057373046875</v>
@@ -615,11 +627,11 @@
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>41.35586166381836</v>
+        <v>41.35586929321289</v>
       </c>
       <c r="C9" t="n">
         <v>77.4091796875</v>
@@ -634,11 +646,11 @@
       <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>41.85129928588867</v>
+        <v>41.85131454467773</v>
       </c>
       <c r="C10" t="n">
         <v>78.33651733398438</v>
@@ -653,11 +665,11 @@
       <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>47.15803146362305</v>
+        <v>47.15805053710938</v>
       </c>
       <c r="C11" t="n">
         <v>88.26959991455078</v>
@@ -672,11 +684,11 @@
       <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>47.10100173950195</v>
+        <v>47.10099029541016</v>
       </c>
       <c r="C12" t="n">
         <v>87.87763214111328</v>
@@ -691,7 +703,7 @@
       <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>39082</v>
       </c>
       <c r="B13" t="n">
@@ -710,11 +722,11 @@
       <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>50.80573654174805</v>
+        <v>50.80572509765625</v>
       </c>
       <c r="C14" t="n">
         <v>94.7896728515625</v>
@@ -729,11 +741,11 @@
       <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>47.76714706420898</v>
+        <v>47.76717376708984</v>
       </c>
       <c r="C15" t="n">
         <v>88.85277557373047</v>
@@ -748,11 +760,11 @@
       <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>48.44559097290039</v>
+        <v>48.44557571411133</v>
       </c>
       <c r="C16" t="n">
         <v>90.11472320556641</v>
@@ -767,11 +779,11 @@
       <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>52.53153228759766</v>
+        <v>52.53155136108398</v>
       </c>
       <c r="C17" t="n">
         <v>97.71510314941406</v>
@@ -786,11 +798,11 @@
       <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>55.00106430053711</v>
+        <v>55.00107192993164</v>
       </c>
       <c r="C18" t="n">
         <v>101.9120483398438</v>
@@ -805,11 +817,11 @@
       <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>54.30452346801758</v>
+        <v>54.30453872680664</v>
       </c>
       <c r="C19" t="n">
         <v>100.6214141845703</v>
@@ -824,11 +836,11 @@
       <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>57.09070205688477</v>
+        <v>57.09068298339844</v>
       </c>
       <c r="C20" t="n">
         <v>105.783935546875</v>
@@ -843,11 +855,11 @@
       <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>60.41994094848633</v>
+        <v>60.41997528076172</v>
       </c>
       <c r="C21" t="n">
         <v>111.5583190917969</v>
@@ -862,11 +874,11 @@
       <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>60.99470520019531</v>
+        <v>60.99469757080078</v>
       </c>
       <c r="C22" t="n">
         <v>112.619499206543</v>
@@ -881,11 +893,11 @@
       <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>60.12483978271484</v>
+        <v>60.12482452392578</v>
       </c>
       <c r="C23" t="n">
         <v>111.0133819580078</v>
@@ -900,11 +912,11 @@
       <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>54.65347290039062</v>
+        <v>54.65345764160156</v>
       </c>
       <c r="C24" t="n">
         <v>100.5544967651367</v>
@@ -919,11 +931,11 @@
       <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>56.17075347900391</v>
+        <v>56.17075729370117</v>
       </c>
       <c r="C25" t="n">
         <v>103.346076965332</v>
@@ -938,11 +950,11 @@
       <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>55.65632247924805</v>
+        <v>55.65634155273438</v>
       </c>
       <c r="C26" t="n">
         <v>102.3996200561523</v>
@@ -957,11 +969,11 @@
       <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>59.38995361328125</v>
+        <v>59.38994979858398</v>
       </c>
       <c r="C27" t="n">
         <v>108.8527755737305</v>
@@ -976,11 +988,11 @@
       <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>60.0576171875</v>
+        <v>60.05760955810547</v>
       </c>
       <c r="C28" t="n">
         <v>110.0764846801758</v>
@@ -995,11 +1007,11 @@
       <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>62.95772933959961</v>
+        <v>62.9577522277832</v>
       </c>
       <c r="C29" t="n">
         <v>115.3919677734375</v>
@@ -1014,11 +1026,11 @@
       <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>67.78732299804688</v>
+        <v>67.78733062744141</v>
       </c>
       <c r="C30" t="n">
         <v>123.7380523681641</v>
@@ -1033,11 +1045,11 @@
       <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>62.07856369018555</v>
+        <v>62.07857513427734</v>
       </c>
       <c r="C31" t="n">
         <v>113.3173980712891</v>
@@ -1052,11 +1064,11 @@
       <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>67.02789306640625</v>
+        <v>67.02790069580078</v>
       </c>
       <c r="C32" t="n">
         <v>122.3518142700195</v>
@@ -1071,11 +1083,11 @@
       <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>64.00284576416016</v>
+        <v>64.00283813476562</v>
       </c>
       <c r="C33" t="n">
         <v>116.3766708374023</v>
@@ -1090,11 +1102,11 @@
       <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>61.49488830566406</v>
+        <v>61.49491119384766</v>
       </c>
       <c r="C34" t="n">
         <v>111.8164443969727</v>
@@ -1109,7 +1121,7 @@
       <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>39752</v>
       </c>
       <c r="B35" t="n">
@@ -1128,11 +1140,11 @@
       <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>43.14326095581055</v>
+        <v>43.14326858520508</v>
       </c>
       <c r="C36" t="n">
         <v>78.011474609375</v>
@@ -1147,11 +1159,11 @@
       <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>44.49679565429688</v>
+        <v>44.49678039550781</v>
       </c>
       <c r="C37" t="n">
         <v>80.45889282226562</v>
@@ -1166,11 +1178,11 @@
       <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>48.45687866210938</v>
+        <v>48.45686340332031</v>
       </c>
       <c r="C38" t="n">
         <v>87.61949920654297</v>
@@ -1185,11 +1197,11 @@
       <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>48.92250061035156</v>
+        <v>48.9224739074707</v>
       </c>
       <c r="C39" t="n">
         <v>87.98279571533203</v>
@@ -1204,11 +1216,11 @@
       <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>51.50601959228516</v>
+        <v>51.50602340698242</v>
       </c>
       <c r="C40" t="n">
         <v>92.62906646728516</v>
@@ -1223,11 +1235,11 @@
       <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>54.86569213867188</v>
+        <v>54.86566925048828</v>
       </c>
       <c r="C41" t="n">
         <v>98.67112731933594</v>
@@ -1242,11 +1254,11 @@
       <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>56.79276657104492</v>
+        <v>56.79278182983398</v>
       </c>
       <c r="C42" t="n">
         <v>101.6061172485352</v>
@@ -1261,11 +1273,11 @@
       <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>55.79885482788086</v>
+        <v>55.79884719848633</v>
       </c>
       <c r="C43" t="n">
         <v>99.82791900634766</v>
@@ -1280,11 +1292,11 @@
       <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>63.0181999206543</v>
+        <v>63.01816558837891</v>
       </c>
       <c r="C44" t="n">
         <v>112.7437896728516</v>
@@ -1305,11 +1317,11 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>63.37654113769531</v>
+        <v>63.37652969360352</v>
       </c>
       <c r="C45" t="n">
         <v>112.8585052490234</v>
@@ -1330,11 +1342,11 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>64.21405792236328</v>
+        <v>64.21404266357422</v>
       </c>
       <c r="C46" t="n">
         <v>114.3499069213867</v>
@@ -1355,11 +1367,11 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>64.75087738037109</v>
+        <v>64.75090026855469</v>
       </c>
       <c r="C47" t="n">
         <v>115.3059234619141</v>
@@ -1380,7 +1392,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>40147</v>
       </c>
       <c r="B48" t="n">
@@ -1405,11 +1417,11 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>70.59058380126953</v>
+        <v>70.590576171875</v>
       </c>
       <c r="C49" t="n">
         <v>125.1434020996094</v>
@@ -1430,11 +1442,11 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>66.00140380859375</v>
+        <v>66.00138854980469</v>
       </c>
       <c r="C50" t="n">
         <v>117.0076446533203</v>
@@ -1455,11 +1467,11 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>68.88043975830078</v>
+        <v>68.88040924072266</v>
       </c>
       <c r="C51" t="n">
         <v>121.5678787231445</v>
@@ -1480,11 +1492,11 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>69.47085571289062</v>
+        <v>69.47088623046875</v>
       </c>
       <c r="C52" t="n">
         <v>122.6099395751953</v>
@@ -1505,11 +1517,11 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>69.87712860107422</v>
+        <v>69.87711334228516</v>
       </c>
       <c r="C53" t="n">
         <v>123.3269577026367</v>
@@ -1530,11 +1542,11 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>68.19901275634766</v>
+        <v>68.19902038574219</v>
       </c>
       <c r="C54" t="n">
         <v>119.7514343261719</v>
@@ -1555,11 +1567,11 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>67.22987365722656</v>
+        <v>67.22988128662109</v>
       </c>
       <c r="C55" t="n">
         <v>118.0497131347656</v>
@@ -1580,7 +1592,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>40390</v>
       </c>
       <c r="B56" t="n">
@@ -1605,11 +1617,11 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>67.37149047851562</v>
+        <v>67.37150573730469</v>
       </c>
       <c r="C57" t="n">
         <v>117.7151031494141</v>
@@ -1630,11 +1642,11 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>73.39572143554688</v>
+        <v>73.39569854736328</v>
       </c>
       <c r="C58" t="n">
         <v>128.2409210205078</v>
@@ -1655,11 +1667,11 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>78.57183074951172</v>
+        <v>78.57185363769531</v>
       </c>
       <c r="C59" t="n">
         <v>137.2848968505859</v>
@@ -1680,11 +1692,11 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>77.74486541748047</v>
+        <v>77.74483489990234</v>
       </c>
       <c r="C60" t="n">
         <v>135.2389984130859</v>
@@ -1705,11 +1717,11 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>80.65769195556641</v>
+        <v>80.65767669677734</v>
       </c>
       <c r="C61" t="n">
         <v>140.3059234619141</v>
@@ -1730,7 +1742,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>40574</v>
       </c>
       <c r="B62" t="n">
@@ -1755,11 +1767,11 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>89.31971740722656</v>
+        <v>89.31970977783203</v>
       </c>
       <c r="C63" t="n">
         <v>154.7610015869141</v>
@@ -1784,11 +1796,11 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>89.97630310058594</v>
+        <v>89.976318359375</v>
       </c>
       <c r="C64" t="n">
         <v>155.8986663818359</v>
@@ -1813,11 +1825,11 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>94.12008666992188</v>
+        <v>94.12007904052734</v>
       </c>
       <c r="C65" t="n">
         <v>163.0783996582031</v>
@@ -1842,11 +1854,11 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>93.62651062011719</v>
+        <v>93.62647247314453</v>
       </c>
       <c r="C66" t="n">
         <v>161.5009613037109</v>
@@ -1871,11 +1883,11 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>95.07858276367188</v>
+        <v>95.07856750488281</v>
       </c>
       <c r="C67" t="n">
         <v>164.0057373046875</v>
@@ -1900,11 +1912,11 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>100.7872009277344</v>
+        <v>100.7871475219727</v>
       </c>
       <c r="C68" t="n">
         <v>173.8527679443359</v>
@@ -1929,11 +1941,11 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>95.69300079345703</v>
+        <v>95.69303894042969</v>
       </c>
       <c r="C69" t="n">
         <v>164.3498992919922</v>
@@ -1958,11 +1970,11 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>97.34068298339844</v>
+        <v>97.34065246582031</v>
       </c>
       <c r="C70" t="n">
         <v>167.1797332763672</v>
@@ -1987,11 +1999,11 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>102.7735214233398</v>
+        <v>102.7735595703125</v>
       </c>
       <c r="C71" t="n">
         <v>176.5105133056641</v>
@@ -2016,11 +2028,11 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>105.0701370239258</v>
+        <v>105.0701293945312</v>
       </c>
       <c r="C72" t="n">
         <v>179.7323150634766</v>
@@ -2045,11 +2057,11 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>102.7675323486328</v>
+        <v>102.767578125</v>
       </c>
       <c r="C73" t="n">
         <v>175.7935028076172</v>
@@ -2074,7 +2086,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>40939</v>
       </c>
       <c r="B74" t="n">
@@ -2103,11 +2115,11 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>110.3773040771484</v>
+        <v>110.3773193359375</v>
       </c>
       <c r="C75" t="n">
         <v>188.0783996582031</v>
@@ -2132,11 +2144,11 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>117.0651397705078</v>
+        <v>117.0651321411133</v>
       </c>
       <c r="C76" t="n">
         <v>199.4741821289062</v>
@@ -2161,11 +2173,11 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>116.1842651367188</v>
+        <v>116.184326171875</v>
       </c>
       <c r="C77" t="n">
         <v>197.9732360839844</v>
@@ -2190,11 +2202,11 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>108.6818695068359</v>
+        <v>108.6818771362305</v>
       </c>
       <c r="C78" t="n">
         <v>184.4168243408203</v>
@@ -2219,11 +2231,11 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>110.1918106079102</v>
+        <v>110.1918334960938</v>
       </c>
       <c r="C79" t="n">
         <v>186.9789733886719</v>
@@ -2248,11 +2260,11 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>110.4171524047852</v>
+        <v>110.4171676635742</v>
       </c>
       <c r="C80" t="n">
         <v>187.3613739013672</v>
@@ -2277,11 +2289,11 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>110.2492446899414</v>
+        <v>110.2491760253906</v>
       </c>
       <c r="C81" t="n">
         <v>186.2810668945312</v>
@@ -2306,11 +2318,11 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>117.3784942626953</v>
+        <v>117.3784866333008</v>
       </c>
       <c r="C82" t="n">
         <v>198.3269653320312</v>
@@ -2335,11 +2347,11 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>110.0682067871094</v>
+        <v>110.0681533813477</v>
       </c>
       <c r="C83" t="n">
         <v>185.9751434326172</v>
@@ -2364,11 +2376,11 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>108.0153198242188</v>
+        <v>108.0153045654297</v>
       </c>
       <c r="C84" t="n">
         <v>181.7112884521484</v>
@@ -2393,11 +2405,11 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>108.8563690185547</v>
+        <v>108.8563232421875</v>
       </c>
       <c r="C85" t="n">
         <v>183.1261901855469</v>
@@ -2422,11 +2434,11 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>115.4030914306641</v>
+        <v>115.403076171875</v>
       </c>
       <c r="C86" t="n">
         <v>194.1395721435547</v>
@@ -2451,11 +2463,11 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>114.6105041503906</v>
+        <v>114.6105499267578</v>
       </c>
       <c r="C87" t="n">
         <v>191.9980926513672</v>
@@ -2480,11 +2492,11 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>121.726921081543</v>
+        <v>121.7269515991211</v>
       </c>
       <c r="C88" t="n">
         <v>203.9196929931641</v>
@@ -2509,11 +2521,11 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>115.5863876342773</v>
+        <v>115.5863723754883</v>
       </c>
       <c r="C89" t="n">
         <v>193.6328887939453</v>
@@ -2538,11 +2550,11 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>119.270149230957</v>
+        <v>119.2701797485352</v>
       </c>
       <c r="C90" t="n">
         <v>198.8718872070312</v>
@@ -2567,7 +2579,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>41455</v>
       </c>
       <c r="B91" t="n">
@@ -2596,11 +2608,11 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>111.8279342651367</v>
+        <v>111.8279800415039</v>
       </c>
       <c r="C92" t="n">
         <v>186.4627075195312</v>
@@ -2625,11 +2637,11 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>105.0286026000977</v>
+        <v>105.0285720825195</v>
       </c>
       <c r="C93" t="n">
         <v>174.2543029785156</v>
@@ -2654,11 +2666,11 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>106.7054214477539</v>
+        <v>106.7053985595703</v>
       </c>
       <c r="C94" t="n">
         <v>177.0363311767578</v>
@@ -2683,11 +2695,11 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>103.2653427124023</v>
+        <v>103.2653503417969</v>
       </c>
       <c r="C95" t="n">
         <v>171.3288726806641</v>
@@ -2712,11 +2724,11 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>104.0921401977539</v>
+        <v>104.0921783447266</v>
       </c>
       <c r="C96" t="n">
         <v>171.7781982421875</v>
@@ -2741,11 +2753,11 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>108.6630096435547</v>
+        <v>108.6630172729492</v>
       </c>
       <c r="C97" t="n">
         <v>179.3212280273438</v>
@@ -2770,11 +2782,11 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>102.3542022705078</v>
+        <v>102.3542404174805</v>
       </c>
       <c r="C98" t="n">
         <v>168.9101409912109</v>
@@ -2799,11 +2811,11 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>107.8607330322266</v>
+        <v>107.8607635498047</v>
       </c>
       <c r="C99" t="n">
         <v>177.0267639160156</v>
@@ -2828,11 +2840,11 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>112.1246032714844</v>
+        <v>112.1246566772461</v>
       </c>
       <c r="C100" t="n">
         <v>184.0248565673828</v>
@@ -2857,11 +2869,11 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>114.4429092407227</v>
+        <v>114.4429550170898</v>
       </c>
       <c r="C101" t="n">
         <v>187.829833984375</v>
@@ -2886,11 +2898,11 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>108.0141525268555</v>
+        <v>108.01416015625</v>
       </c>
       <c r="C102" t="n">
         <v>176.2523956298828</v>
@@ -2915,11 +2927,11 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>106.2037811279297</v>
+        <v>106.2037506103516</v>
       </c>
       <c r="C103" t="n">
         <v>173.2982788085938</v>
@@ -2944,7 +2956,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="B104" t="n">
@@ -2973,11 +2985,11 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>113.3324508666992</v>
+        <v>113.3323974609375</v>
       </c>
       <c r="C105" t="n">
         <v>183.8432159423828</v>
@@ -3002,11 +3014,11 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>111.8767013549805</v>
+        <v>111.8766860961914</v>
       </c>
       <c r="C106" t="n">
         <v>181.4818420410156</v>
@@ -3031,11 +3043,11 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>96.88947296142578</v>
+        <v>96.88950347900391</v>
       </c>
       <c r="C107" t="n">
         <v>157.170166015625</v>
@@ -3060,11 +3072,11 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>96.22933959960938</v>
+        <v>96.22937774658203</v>
       </c>
       <c r="C108" t="n">
         <v>155.0382385253906</v>
@@ -3089,11 +3101,11 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>95.20280456542969</v>
+        <v>95.20281219482422</v>
       </c>
       <c r="C109" t="n">
         <v>153.3843231201172</v>
@@ -3118,11 +3130,11 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>90.97200012207031</v>
+        <v>90.97196197509766</v>
       </c>
       <c r="C110" t="n">
         <v>146.56787109375</v>
@@ -3147,11 +3159,11 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>96.76698303222656</v>
+        <v>96.76696014404297</v>
       </c>
       <c r="C111" t="n">
         <v>154.818359375</v>
@@ -3176,11 +3188,11 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>95.90648651123047</v>
+        <v>95.906494140625</v>
       </c>
       <c r="C112" t="n">
         <v>153.4416809082031</v>
@@ -3205,11 +3217,11 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>102.3540267944336</v>
+        <v>102.3540573120117</v>
       </c>
       <c r="C113" t="n">
         <v>163.7571716308594</v>
@@ -3234,11 +3246,11 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>102.1412582397461</v>
+        <v>102.1412506103516</v>
       </c>
       <c r="C114" t="n">
         <v>162.1893005371094</v>
@@ -3263,11 +3275,11 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>97.93273162841797</v>
+        <v>97.93276977539062</v>
       </c>
       <c r="C115" t="n">
         <v>155.5066986083984</v>
@@ -3292,11 +3304,11 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>97.52938079833984</v>
+        <v>97.52938842773438</v>
       </c>
       <c r="C116" t="n">
         <v>154.8661499023438</v>
@@ -3321,11 +3333,11 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>89.77935791015625</v>
+        <v>89.77934265136719</v>
       </c>
       <c r="C117" t="n">
         <v>141.38623046875</v>
@@ -3350,11 +3362,11 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>88.00672149658203</v>
+        <v>88.00670623779297</v>
       </c>
       <c r="C118" t="n">
         <v>138.5946502685547</v>
@@ -3379,11 +3391,11 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>85.03813934326172</v>
+        <v>85.03812408447266</v>
       </c>
       <c r="C119" t="n">
         <v>133.9196929931641</v>
@@ -3408,11 +3420,11 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>85.43138885498047</v>
+        <v>85.431396484375</v>
       </c>
       <c r="C120" t="n">
         <v>133.2887115478516</v>
@@ -3437,11 +3449,11 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>84.32842254638672</v>
+        <v>84.32840728759766</v>
       </c>
       <c r="C121" t="n">
         <v>131.56787109375</v>
@@ -3466,11 +3478,11 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>76.4666748046875</v>
+        <v>76.46665191650391</v>
       </c>
       <c r="C122" t="n">
         <v>119.3021011352539</v>
@@ -3495,11 +3507,11 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>81.11043548583984</v>
+        <v>81.11045074462891</v>
       </c>
       <c r="C123" t="n">
         <v>125.2676849365234</v>
@@ -3524,11 +3536,11 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>93.75086212158203</v>
+        <v>93.7508544921875</v>
       </c>
       <c r="C124" t="n">
         <v>144.7896728515625</v>
@@ -3553,11 +3565,11 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>90.34006500244141</v>
+        <v>90.34008026123047</v>
       </c>
       <c r="C125" t="n">
         <v>139.5219879150391</v>
@@ -3582,11 +3594,11 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>96.08689117431641</v>
+        <v>96.08682250976562</v>
       </c>
       <c r="C126" t="n">
         <v>146.9789733886719</v>
@@ -3611,11 +3623,11 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>94.86187744140625</v>
+        <v>94.86184692382812</v>
       </c>
       <c r="C127" t="n">
         <v>145.1051635742188</v>
@@ -3640,7 +3652,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>42582</v>
       </c>
       <c r="B128" t="n">
@@ -3669,11 +3681,11 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>100.1569442749023</v>
+        <v>100.1569290161133</v>
       </c>
       <c r="C129" t="n">
         <v>151.8929290771484</v>
@@ -3698,11 +3710,11 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>100.1380233764648</v>
+        <v>100.1380386352539</v>
       </c>
       <c r="C130" t="n">
         <v>151.8642425537109</v>
@@ -3727,11 +3739,11 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>96.88518524169922</v>
+        <v>96.88520812988281</v>
       </c>
       <c r="C131" t="n">
         <v>146.9311676025391</v>
@@ -3756,11 +3768,11 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>103.1902084350586</v>
+        <v>103.1901702880859</v>
       </c>
       <c r="C132" t="n">
         <v>155.0860443115234</v>
@@ -3785,11 +3797,11 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>105.5883331298828</v>
+        <v>105.5883255004883</v>
       </c>
       <c r="C133" t="n">
         <v>158.6902465820312</v>
@@ -3814,11 +3826,11 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>111.0143890380859</v>
+        <v>111.0143966674805</v>
       </c>
       <c r="C134" t="n">
         <v>166.8451232910156</v>
@@ -3843,11 +3855,11 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>115.2901992797852</v>
+        <v>115.2902145385742</v>
       </c>
       <c r="C135" t="n">
         <v>171.9120483398438</v>
@@ -3872,11 +3884,11 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>111.6485290527344</v>
+        <v>111.6485137939453</v>
       </c>
       <c r="C136" t="n">
         <v>166.4818420410156</v>
@@ -3901,11 +3913,11 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>102.7687072753906</v>
+        <v>102.768669128418</v>
       </c>
       <c r="C137" t="n">
         <v>153.2409210205078</v>
@@ -3930,7 +3942,7 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>42886</v>
       </c>
       <c r="B138" t="n">
@@ -3959,7 +3971,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B139" t="n">
@@ -3988,11 +4000,11 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>93.66016387939453</v>
+        <v>93.66015625</v>
       </c>
       <c r="C140" t="n">
         <v>138.3078460693359</v>
@@ -4017,7 +4029,7 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="B141" t="n">
@@ -4046,11 +4058,11 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>94.91796875</v>
+        <v>94.91797637939453</v>
       </c>
       <c r="C142" t="n">
         <v>138.6998138427734</v>
@@ -4075,11 +4087,11 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>100.7931137084961</v>
+        <v>100.7930679321289</v>
       </c>
       <c r="C143" t="n">
         <v>147.2848968505859</v>
@@ -4104,11 +4116,11 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>101.7410659790039</v>
+        <v>101.7410736083984</v>
       </c>
       <c r="C144" t="n">
         <v>147.1988525390625</v>
@@ -4133,11 +4145,11 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>101.3776397705078</v>
+        <v>101.3776473999023</v>
       </c>
       <c r="C145" t="n">
         <v>146.6730346679688</v>
@@ -4162,7 +4174,7 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="B146" t="n">
@@ -4191,11 +4203,11 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>103.9839782714844</v>
+        <v>103.9839706420898</v>
       </c>
       <c r="C147" t="n">
         <v>148.97705078125</v>
@@ -4220,11 +4232,11 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>102.382438659668</v>
+        <v>102.3824691772461</v>
       </c>
       <c r="C148" t="n">
         <v>146.6826019287109</v>
@@ -4249,11 +4261,11 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>96.73049926757812</v>
+        <v>96.73050689697266</v>
       </c>
       <c r="C149" t="n">
         <v>138.5850830078125</v>
@@ -4278,11 +4290,11 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>95.34165191650391</v>
+        <v>95.34165954589844</v>
       </c>
       <c r="C150" t="n">
         <v>135.0955963134766</v>
@@ -4307,11 +4319,11 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>94.25537872314453</v>
+        <v>94.25539398193359</v>
       </c>
       <c r="C151" t="n">
         <v>133.5564117431641</v>
@@ -4336,11 +4348,11 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>97.78404998779297</v>
+        <v>97.78408050537109</v>
       </c>
       <c r="C152" t="n">
         <v>138.5564117431641</v>
@@ -4365,11 +4377,11 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>99.89756774902344</v>
+        <v>99.89759063720703</v>
       </c>
       <c r="C153" t="n">
         <v>140.0382385253906</v>
@@ -4394,11 +4406,11 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>103.1233367919922</v>
+        <v>103.1233901977539</v>
       </c>
       <c r="C154" t="n">
         <v>144.5602264404297</v>
@@ -4423,7 +4435,7 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="B155" t="n">
@@ -4452,7 +4464,7 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B156" t="n">
@@ -4481,11 +4493,11 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>78.50888824462891</v>
+        <v>78.50887298583984</v>
       </c>
       <c r="C157" t="n">
         <v>108.6711273193359</v>
@@ -4510,11 +4522,11 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>92.84035491943359</v>
+        <v>92.84037017822266</v>
       </c>
       <c r="C158" t="n">
         <v>128.5086059570312</v>
@@ -4539,11 +4551,11 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>96.51431274414062</v>
+        <v>96.51432037353516</v>
       </c>
       <c r="C159" t="n">
         <v>132.0554504394531</v>
@@ -4568,11 +4580,11 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>98.58954620361328</v>
+        <v>98.58953094482422</v>
       </c>
       <c r="C160" t="n">
         <v>134.8948364257812</v>
@@ -4597,11 +4609,11 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>98.00958251953125</v>
+        <v>98.00959014892578</v>
       </c>
       <c r="C161" t="n">
         <v>134.1013336181641</v>
@@ -4626,7 +4638,7 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B162" t="n">
@@ -4655,7 +4667,7 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B163" t="n">
@@ -4684,11 +4696,11 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>104.8087615966797</v>
+        <v>104.8087692260742</v>
       </c>
       <c r="C164" t="n">
         <v>141.7208404541016</v>
@@ -4713,11 +4725,11 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>96.95158386230469</v>
+        <v>96.95157623291016</v>
       </c>
       <c r="C165" t="n">
         <v>129.5697937011719</v>
@@ -4742,7 +4754,7 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B166" t="n">
@@ -4771,11 +4783,11 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>95.66393280029297</v>
+        <v>95.6639404296875</v>
       </c>
       <c r="C167" t="n">
         <v>127.8489456176758</v>
@@ -4800,11 +4812,11 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>97.31496429443359</v>
+        <v>97.31497955322266</v>
       </c>
       <c r="C168" t="n">
         <v>128.5372924804688</v>
@@ -4829,11 +4841,11 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>97.01819610595703</v>
+        <v>97.01820373535156</v>
       </c>
       <c r="C169" t="n">
         <v>128.1453094482422</v>
@@ -4858,11 +4870,11 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>104.0318374633789</v>
+        <v>104.0318450927734</v>
       </c>
       <c r="C170" t="n">
         <v>137.4091796875</v>
@@ -4887,11 +4899,11 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>95.18631744384766</v>
+        <v>95.18630218505859</v>
       </c>
       <c r="C171" t="n">
         <v>124.426383972168</v>
@@ -4916,11 +4928,11 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>81.12957763671875</v>
+        <v>81.12960052490234</v>
       </c>
       <c r="C172" t="n">
         <v>106.051628112793</v>
@@ -4945,11 +4957,11 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>91.82937622070312</v>
+        <v>91.82938385009766</v>
       </c>
       <c r="C173" t="n">
         <v>120.0382385253906</v>
@@ -4974,11 +4986,11 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>92.57173919677734</v>
+        <v>92.57172393798828</v>
       </c>
       <c r="C174" t="n">
         <v>119.4072647094727</v>
@@ -5003,11 +5015,11 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>89.5107421875</v>
+        <v>89.51071929931641</v>
       </c>
       <c r="C175" t="n">
         <v>115.4588928222656</v>
@@ -5032,11 +5044,11 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>91.11904907226562</v>
+        <v>91.11905670166016</v>
       </c>
       <c r="C176" t="n">
         <v>117.5334625244141</v>
@@ -5061,11 +5073,11 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>92.58993530273438</v>
+        <v>92.58992004394531</v>
       </c>
       <c r="C177" t="n">
         <v>117.8871917724609</v>
@@ -5090,11 +5102,11 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>91.35850524902344</v>
+        <v>91.3585205078125</v>
       </c>
       <c r="C178" t="n">
         <v>116.3193130493164</v>
@@ -5119,11 +5131,11 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>83.84227752685547</v>
+        <v>83.84229278564453</v>
       </c>
       <c r="C179" t="n">
         <v>106.7495193481445</v>
@@ -5148,7 +5160,7 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B180" t="n">
@@ -5177,7 +5189,7 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B181" t="n">
@@ -5206,11 +5218,11 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>90.73313140869141</v>
+        <v>90.73314666748047</v>
       </c>
       <c r="C182" t="n">
         <v>113.8718948364258</v>
@@ -5235,11 +5247,11 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>91.80664825439453</v>
+        <v>91.806640625</v>
       </c>
       <c r="C183" t="n">
         <v>113.6998062133789</v>
@@ -5264,11 +5276,11 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>102.8685073852539</v>
+        <v>102.8685531616211</v>
       </c>
       <c r="C184" t="n">
         <v>127.3996200561523</v>
@@ -5293,11 +5305,11 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>109.5226287841797</v>
+        <v>109.5226516723633</v>
       </c>
       <c r="C185" t="n">
         <v>135.6405334472656</v>
@@ -5322,11 +5334,11 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>112.1981811523438</v>
+        <v>112.1981964111328</v>
       </c>
       <c r="C186" t="n">
         <v>137.4187316894531</v>
@@ -5351,11 +5363,11 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>114.4227905273438</v>
+        <v>114.4228210449219</v>
       </c>
       <c r="C187" t="n">
         <v>140.1434020996094</v>
@@ -5380,11 +5392,11 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>110.0282287597656</v>
+        <v>110.0282440185547</v>
       </c>
       <c r="C188" t="n">
         <v>134.7610015869141</v>
@@ -5409,11 +5421,11 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>110.8054504394531</v>
+        <v>110.8054733276367</v>
       </c>
       <c r="C189" t="n">
         <v>134.1682586669922</v>
@@ -5438,7 +5450,7 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B190" t="n">
@@ -5467,11 +5479,11 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>98.772705078125</v>
+        <v>98.77271270751953</v>
       </c>
       <c r="C191" t="n">
         <v>119.5984725952148</v>
@@ -5496,7 +5508,7 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B192" t="n">
@@ -5525,7 +5537,7 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B193" t="n">
@@ -5554,11 +5566,11 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>111.7833862304688</v>
+        <v>111.7834091186523</v>
       </c>
       <c r="C194" t="n">
         <v>133.5700073242188</v>
@@ -5583,11 +5595,11 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>103.7623748779297</v>
+        <v>103.7623825073242</v>
       </c>
       <c r="C195" t="n">
         <v>122.5100021362305</v>
@@ -5612,7 +5624,7 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B196" t="n">
@@ -5641,11 +5653,11 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>111.9779891967773</v>
+        <v>111.97802734375</v>
       </c>
       <c r="C197" t="n">
         <v>132.2100067138672</v>
@@ -5670,11 +5682,11 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>119.0198822021484</v>
+        <v>119.0198974609375</v>
       </c>
       <c r="C198" t="n">
         <v>138.8399963378906</v>
@@ -5699,11 +5711,11 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>121.0344314575195</v>
+        <v>121.034423828125</v>
       </c>
       <c r="C199" t="n">
         <v>141.1900024414062</v>
@@ -5728,11 +5740,11 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>112.1190567016602</v>
+        <v>112.1190643310547</v>
       </c>
       <c r="C200" t="n">
         <v>130.7899932861328</v>
@@ -5757,11 +5769,11 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>111.5004501342773</v>
+        <v>111.5004577636719</v>
       </c>
       <c r="C201" t="n">
         <v>128.4499969482422</v>
@@ -5786,11 +5798,11 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>103.1325073242188</v>
+        <v>103.1324996948242</v>
       </c>
       <c r="C202" t="n">
         <v>118.8099975585938</v>
@@ -5815,11 +5827,11 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>120.0419998168945</v>
+        <v>120.0420227050781</v>
       </c>
       <c r="C203" t="n">
         <v>138.2899932861328</v>
@@ -5844,11 +5856,11 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>130.7930145263672</v>
+        <v>130.7930603027344</v>
       </c>
       <c r="C204" t="n">
         <v>148.8999938964844</v>
@@ -5873,11 +5885,11 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>123.7571105957031</v>
+        <v>123.7571029663086</v>
       </c>
       <c r="C205" t="n">
         <v>140.8899993896484</v>
@@ -5902,11 +5914,11 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>118.3461990356445</v>
+        <v>118.3461761474609</v>
       </c>
       <c r="C206" t="n">
         <v>134.7299957275391</v>
@@ -5931,11 +5943,11 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>114.9715881347656</v>
+        <v>114.9715805053711</v>
       </c>
       <c r="C207" t="n">
         <v>129.3000030517578</v>
@@ -5960,7 +5972,7 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B208" t="n">
@@ -5989,7 +6001,7 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B209" t="n">
@@ -6018,11 +6030,11 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>115.8993453979492</v>
+        <v>115.8993530273438</v>
       </c>
       <c r="C210" t="n">
         <v>128.5899963378906</v>
@@ -6047,11 +6059,11 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>120.6041793823242</v>
+        <v>120.6041946411133</v>
       </c>
       <c r="C211" t="n">
         <v>133.8099975585938</v>
@@ -6076,11 +6088,11 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>129.9507446289062</v>
+        <v>129.9507598876953</v>
       </c>
       <c r="C212" t="n">
         <v>144.1799926757812</v>
@@ -6105,7 +6117,7 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B213" t="n">
@@ -6134,7 +6146,7 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B214" t="n">
@@ -6163,11 +6175,11 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>131.8655700683594</v>
+        <v>131.8656005859375</v>
       </c>
       <c r="C215" t="n">
         <v>144.6399993896484</v>
@@ -6192,11 +6204,11 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>146.1956176757812</v>
+        <v>146.1956024169922</v>
       </c>
       <c r="C216" t="n">
         <v>158.5599975585938</v>
@@ -6221,7 +6233,7 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B217" t="n">
@@ -6250,7 +6262,7 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B218" t="n">
@@ -6279,11 +6291,11 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>172.1568603515625</v>
+        <v>172.1568756103516</v>
       </c>
       <c r="C219" t="n">
         <v>185.0299987792969</v>
@@ -6308,11 +6320,11 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B220" t="n">
-        <v>177.67431640625</v>
+        <v>177.6742858886719</v>
       </c>
       <c r="C220" t="n">
         <v>190.9600067138672</v>
@@ -6337,7 +6349,7 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B221" t="n">
@@ -6366,11 +6378,11 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B222" t="n">
-        <v>156.7827453613281</v>
+        <v>156.7827758789062</v>
       </c>
       <c r="C222" t="n">
         <v>166.8500061035156</v>
@@ -6395,11 +6407,11 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>162.5147094726562</v>
+        <v>162.5146942138672</v>
       </c>
       <c r="C223" t="n">
         <v>172.9499969482422</v>
@@ -6424,11 +6436,11 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>180.5468444824219</v>
+        <v>180.5468139648438</v>
       </c>
       <c r="C224" t="n">
         <v>192.1399993896484</v>
@@ -6453,7 +6465,7 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B225" t="n">
@@ -6482,11 +6494,11 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B226" t="n">
-        <v>209.5576477050781</v>
+        <v>209.5576324462891</v>
       </c>
       <c r="C226" t="n">
         <v>221.0800018310547</v>
@@ -6511,7 +6523,7 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B227" t="n">
@@ -6540,7 +6552,7 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B228" t="n">
@@ -6569,11 +6581,11 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B229" t="n">
-        <v>210.0149993896484</v>
+        <v>210.0149841308594</v>
       </c>
       <c r="C229" t="n">
         <v>219.8300018310547</v>
@@ -6598,11 +6610,11 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B230" t="n">
-        <v>244.2834625244141</v>
+        <v>244.283447265625</v>
       </c>
       <c r="C230" t="n">
         <v>255.6999969482422</v>
@@ -6627,11 +6639,11 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B231" t="n">
-        <v>242.7757110595703</v>
+        <v>242.7757415771484</v>
       </c>
       <c r="C231" t="n">
         <v>252.4400024414062</v>
@@ -6656,11 +6668,11 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B232" t="n">
-        <v>239.1404571533203</v>
+        <v>239.1404418945312</v>
       </c>
       <c r="C232" t="n">
         <v>248.6600036621094</v>
@@ -6685,11 +6697,11 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B233" t="n">
-        <v>232.5623016357422</v>
+        <v>232.5623168945312</v>
       </c>
       <c r="C233" t="n">
         <v>241.8200073242188</v>
@@ -6714,11 +6726,11 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B234" t="n">
-        <v>250.8001861572266</v>
+        <v>250.8002014160156</v>
       </c>
       <c r="C234" t="n">
         <v>259.0599975585938</v>
@@ -6743,11 +6755,11 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B235" t="n">
-        <v>285.3813171386719</v>
+        <v>285.38134765625</v>
       </c>
       <c r="C235" t="n">
         <v>294.7799987792969</v>
@@ -6772,11 +6784,11 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B236" t="n">
-        <v>245.0786285400391</v>
+        <v>245.0786437988281</v>
       </c>
       <c r="C236" t="n">
         <v>253.1499938964844</v>
@@ -6801,11 +6813,11 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B237" t="n">
-        <v>237.3204345703125</v>
+        <v>237.3204040527344</v>
       </c>
       <c r="C237" t="n">
         <v>243.4900054931641</v>
@@ -6830,11 +6842,11 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B238" t="n">
-        <v>275.0106201171875</v>
+        <v>275.0105895996094</v>
       </c>
       <c r="C238" t="n">
         <v>282.1600036621094</v>
@@ -6859,11 +6871,11 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B239" t="n">
-        <v>299.6208190917969</v>
+        <v>299.6207885742188</v>
       </c>
       <c r="C239" t="n">
         <v>307.4100036621094</v>
@@ -6888,7 +6900,7 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B240" t="n">
@@ -6917,11 +6929,11 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B241" t="n">
-        <v>290.2964172363281</v>
+        <v>290.29638671875</v>
       </c>
       <c r="C241" t="n">
         <v>296.2099914550781</v>
@@ -6946,7 +6958,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B242" t="n">
@@ -6975,11 +6987,11 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B243" t="n">
-        <v>236.7566070556641</v>
+        <v>236.7566223144531</v>
       </c>
       <c r="C243" t="n">
         <v>240.2100067138672</v>
@@ -7004,7 +7016,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B244" t="n">
@@ -7033,11 +7045,11 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B245" t="n">
-        <v>227.6593017578125</v>
+        <v>227.6592864990234</v>
       </c>
       <c r="C245" t="n">
         <v>230.9799957275391</v>
@@ -7062,7 +7074,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B246" t="n">
@@ -7091,7 +7103,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B247" t="n">
@@ -7120,7 +7132,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B248" t="n">
@@ -7149,7 +7161,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B249" t="n">
@@ -7178,32 +7190,32 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B250" t="n">
-        <v>232.7599945068359</v>
+        <v>227.0599975585938</v>
       </c>
       <c r="C250" t="n">
-        <v>232.7599945068359</v>
+        <v>227.0599975585938</v>
       </c>
       <c r="D250" t="n">
-        <v>92409400</v>
+        <v>96551800</v>
       </c>
       <c r="E250" t="n">
         <v>11.29</v>
       </c>
       <c r="F250" t="n">
-        <v>20.61647426987032</v>
+        <v>20.11160297241752</v>
       </c>
       <c r="G250" t="n">
         <v>942134390</v>
       </c>
       <c r="H250" t="n">
-        <v>219291195441.1012</v>
+        <v>213921032293.2672</v>
       </c>
       <c r="I250" t="n">
-        <v>0.09808515746888297</v>
+        <v>0.1024819824271567</v>
       </c>
     </row>
   </sheetData>
@@ -7235,75 +7247,75 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>eps_trimestral</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>filed_ttm</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39539</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>39629</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>40022</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -7339,13 +7351,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>39630</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>39721</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>40113</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -7381,13 +7393,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>39814</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>39903</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>40295</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -7423,13 +7435,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>39904</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>39994</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>40022</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -7465,13 +7477,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>39995</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40086</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>40113</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -7507,13 +7519,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40179</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40268</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>40295</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -7549,13 +7561,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40269</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40359</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>40386</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -7591,13 +7603,13 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40360</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40451</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="2" t="n">
         <v>40477</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -7633,13 +7645,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40452</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40543</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="2" t="n">
         <v>40596</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -7666,7 +7678,7 @@
       <c r="I10" t="n">
         <v>11.01338432122371</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="2" t="n">
         <v>40596</v>
       </c>
       <c r="K10" t="n">
@@ -7679,13 +7691,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40544</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40633</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <v>40659</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -7712,7 +7724,7 @@
       <c r="I11" t="n">
         <v>11.33843212237094</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="2" t="n">
         <v>40659</v>
       </c>
       <c r="K11" t="n">
@@ -7725,13 +7737,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40634</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40724</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="2" t="n">
         <v>40750</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -7758,7 +7770,7 @@
       <c r="I12" t="n">
         <v>11.7112810707457</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="J12" s="2" t="n">
         <v>40750</v>
       </c>
       <c r="K12" t="n">
@@ -7771,13 +7783,13 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>40725</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>40816</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="2" t="n">
         <v>40841</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -7804,7 +7816,7 @@
       <c r="I13" t="n">
         <v>12.06500956022944</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13" s="2" t="n">
         <v>40841</v>
       </c>
       <c r="K13" t="n">
@@ -7817,13 +7829,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>40817</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>40908</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="2" t="n">
         <v>40967</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -7850,7 +7862,7 @@
       <c r="I14" t="n">
         <v>12.48565965583174</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="J14" s="2" t="n">
         <v>40967</v>
       </c>
       <c r="K14" t="n">
@@ -7863,13 +7875,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>40909</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>40999</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="2" t="n">
         <v>41023</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -7896,7 +7908,7 @@
       <c r="I15" t="n">
         <v>12.77246653919694</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="J15" s="2" t="n">
         <v>41023</v>
       </c>
       <c r="K15" t="n">
@@ -7909,13 +7921,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41000</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41090</v>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" s="2" t="n">
         <v>41121</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -7942,7 +7954,7 @@
       <c r="I16" t="n">
         <v>13.09751434034417</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" s="2" t="n">
         <v>41121</v>
       </c>
       <c r="K16" t="n">
@@ -7955,13 +7967,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41091</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41182</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="2" t="n">
         <v>41212</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -7988,7 +8000,7 @@
       <c r="I17" t="n">
         <v>13.23135755258126</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="J17" s="2" t="n">
         <v>41212</v>
       </c>
       <c r="K17" t="n">
@@ -8001,13 +8013,13 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41183</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41274</v>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" s="2" t="n">
         <v>41331</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -8034,7 +8046,7 @@
       <c r="I18" t="n">
         <v>13.73804971319312</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="J18" s="2" t="n">
         <v>41331</v>
       </c>
       <c r="K18" t="n">
@@ -8047,13 +8059,13 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41275</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41364</v>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -8080,7 +8092,7 @@
       <c r="I19" t="n">
         <v>13.82409177820268</v>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="K19" t="n">
@@ -8093,13 +8105,13 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41365</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41455</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -8126,7 +8138,7 @@
       <c r="I20" t="n">
         <v>13.41300191204589</v>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="J20" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="K20" t="n">
@@ -8139,13 +8151,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41456</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41547</v>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" s="2" t="n">
         <v>41576</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -8172,7 +8184,7 @@
       <c r="I21" t="n">
         <v>13.74760994263862</v>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" s="2" t="n">
         <v>41576</v>
       </c>
       <c r="K21" t="n">
@@ -8185,13 +8197,13 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41548</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41639</v>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" s="2" t="n">
         <v>41695</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -8218,7 +8230,7 @@
       <c r="I22" t="n">
         <v>14.282982791587</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="J22" s="2" t="n">
         <v>41695</v>
       </c>
       <c r="K22" t="n">
@@ -8231,13 +8243,13 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41640</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41729</v>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="2" t="n">
         <v>41758</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -8264,7 +8276,7 @@
       <c r="I23" t="n">
         <v>13.89101338432122</v>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="J23" s="2" t="n">
         <v>41758</v>
       </c>
       <c r="K23" t="n">
@@ -8277,13 +8289,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>41730</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>41820</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="2" t="n">
         <v>41849</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -8310,7 +8322,7 @@
       <c r="I24" t="n">
         <v>15.04780114722753</v>
       </c>
-      <c r="J24" s="1" t="n">
+      <c r="J24" s="2" t="n">
         <v>41849</v>
       </c>
       <c r="K24" t="n">
@@ -8323,13 +8335,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>41821</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>41912</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" s="2" t="n">
         <v>41940</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -8356,7 +8368,7 @@
       <c r="I25" t="n">
         <v>11.54875717017208</v>
       </c>
-      <c r="J25" s="1" t="n">
+      <c r="J25" s="2" t="n">
         <v>41940</v>
       </c>
       <c r="K25" t="n">
@@ -8369,13 +8381,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>41913</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42004</v>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" s="2" t="n">
         <v>42059</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -8402,7 +8414,7 @@
       <c r="I26" t="n">
         <v>11.37667304015296</v>
       </c>
-      <c r="J26" s="1" t="n">
+      <c r="J26" s="2" t="n">
         <v>42059</v>
       </c>
       <c r="K26" t="n">
@@ -8415,13 +8427,13 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42005</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42094</v>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" s="2" t="n">
         <v>42122</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -8448,7 +8460,7 @@
       <c r="I27" t="n">
         <v>11.434034416826</v>
       </c>
-      <c r="J27" s="1" t="n">
+      <c r="J27" s="2" t="n">
         <v>42122</v>
       </c>
       <c r="K27" t="n">
@@ -8461,13 +8473,13 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42095</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42185</v>
       </c>
-      <c r="C28" s="1" t="n">
+      <c r="C28" s="2" t="n">
         <v>42213</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -8494,7 +8506,7 @@
       <c r="I28" t="n">
         <v>10.84130019120459</v>
       </c>
-      <c r="J28" s="1" t="n">
+      <c r="J28" s="2" t="n">
         <v>42213</v>
       </c>
       <c r="K28" t="n">
@@ -8507,13 +8519,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42186</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42277</v>
       </c>
-      <c r="C29" s="1" t="n">
+      <c r="C29" s="2" t="n">
         <v>42304</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -8540,7 +8552,7 @@
       <c r="I29" t="n">
         <v>13.69980879541109</v>
       </c>
-      <c r="J29" s="1" t="n">
+      <c r="J29" s="2" t="n">
         <v>42304</v>
       </c>
       <c r="K29" t="n">
@@ -8553,13 +8565,13 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42278</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42369</v>
       </c>
-      <c r="C30" s="1" t="n">
+      <c r="C30" s="2" t="n">
         <v>42423</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -8586,7 +8598,7 @@
       <c r="I30" t="n">
         <v>12.82982791586998</v>
       </c>
-      <c r="J30" s="1" t="n">
+      <c r="J30" s="2" t="n">
         <v>42423</v>
       </c>
       <c r="K30" t="n">
@@ -8599,13 +8611,13 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42370</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42460</v>
       </c>
-      <c r="C31" s="1" t="n">
+      <c r="C31" s="2" t="n">
         <v>42486</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -8632,7 +8644,7 @@
       <c r="I31" t="n">
         <v>12.58126195028681</v>
       </c>
-      <c r="J31" s="1" t="n">
+      <c r="J31" s="2" t="n">
         <v>42486</v>
       </c>
       <c r="K31" t="n">
@@ -8645,13 +8657,13 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42461</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42551</v>
       </c>
-      <c r="C32" s="1" t="n">
+      <c r="C32" s="2" t="n">
         <v>42577</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -8678,7 +8690,7 @@
       <c r="I32" t="n">
         <v>11.73040152963671</v>
       </c>
-      <c r="J32" s="1" t="n">
+      <c r="J32" s="2" t="n">
         <v>42577</v>
       </c>
       <c r="K32" t="n">
@@ -8691,13 +8703,13 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42552</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42643</v>
       </c>
-      <c r="C33" s="1" t="n">
+      <c r="C33" s="2" t="n">
         <v>42668</v>
       </c>
       <c r="D33" t="inlineStr">
@@ -8724,7 +8736,7 @@
       <c r="I33" t="n">
         <v>11.70172084130019</v>
       </c>
-      <c r="J33" s="1" t="n">
+      <c r="J33" s="2" t="n">
         <v>42668</v>
       </c>
       <c r="K33" t="n">
@@ -8737,13 +8749,13 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42644</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42735</v>
       </c>
-      <c r="C34" s="1" t="n">
+      <c r="C34" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="D34" t="inlineStr">
@@ -8770,7 +8782,7 @@
       <c r="I34" t="n">
         <v>11.83556405353728</v>
       </c>
-      <c r="J34" s="1" t="n">
+      <c r="J34" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="K34" t="n">
@@ -8783,13 +8795,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>42736</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>42825</v>
       </c>
-      <c r="C35" s="1" t="n">
+      <c r="C35" s="2" t="n">
         <v>42850</v>
       </c>
       <c r="D35" t="inlineStr">
@@ -8816,7 +8828,7 @@
       <c r="I35" t="n">
         <v>11.60611854684512</v>
       </c>
-      <c r="J35" s="1" t="n">
+      <c r="J35" s="2" t="n">
         <v>42850</v>
       </c>
       <c r="K35" t="n">
@@ -8829,13 +8841,13 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>42826</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>42916</v>
       </c>
-      <c r="C36" s="1" t="n">
+      <c r="C36" s="2" t="n">
         <v>42941</v>
       </c>
       <c r="D36" t="inlineStr">
@@ -8862,7 +8874,7 @@
       <c r="I36" t="n">
         <v>11.48183556405354</v>
       </c>
-      <c r="J36" s="1" t="n">
+      <c r="J36" s="2" t="n">
         <v>42941</v>
       </c>
       <c r="K36" t="n">
@@ -8875,13 +8887,13 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>42917</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43008</v>
       </c>
-      <c r="C37" s="1" t="n">
+      <c r="C37" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="D37" t="inlineStr">
@@ -8908,7 +8920,7 @@
       <c r="I37" t="n">
         <v>11.4244741873805</v>
       </c>
-      <c r="J37" s="1" t="n">
+      <c r="J37" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="K37" t="n">
@@ -8921,13 +8933,13 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43009</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43100</v>
       </c>
-      <c r="C38" s="1" t="n">
+      <c r="C38" s="2" t="n">
         <v>43158</v>
       </c>
       <c r="D38" t="inlineStr">
@@ -8954,7 +8966,7 @@
       <c r="I38" t="n">
         <v>5.869980879541108</v>
       </c>
-      <c r="J38" s="1" t="n">
+      <c r="J38" s="2" t="n">
         <v>43158</v>
       </c>
       <c r="K38" t="n">
@@ -8967,13 +8979,13 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43101</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43190</v>
       </c>
-      <c r="C39" s="1" t="n">
+      <c r="C39" s="2" t="n">
         <v>43214</v>
       </c>
       <c r="D39" t="inlineStr">
@@ -9000,7 +9012,7 @@
       <c r="I39" t="n">
         <v>5.831739961759082</v>
       </c>
-      <c r="J39" s="1" t="n">
+      <c r="J39" s="2" t="n">
         <v>43214</v>
       </c>
       <c r="K39" t="n">
@@ -9013,13 +9025,13 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43191</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43281</v>
       </c>
-      <c r="C40" s="1" t="n">
+      <c r="C40" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="D40" t="inlineStr">
@@ -9046,7 +9058,7 @@
       <c r="I40" t="n">
         <v>5.956022944550669</v>
       </c>
-      <c r="J40" s="1" t="n">
+      <c r="J40" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="K40" t="n">
@@ -9059,13 +9071,13 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43282</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43373</v>
       </c>
-      <c r="C41" s="1" t="n">
+      <c r="C41" s="2" t="n">
         <v>43403</v>
       </c>
       <c r="D41" t="inlineStr">
@@ -9092,7 +9104,7 @@
       <c r="I41" t="n">
         <v>5.975143403441683</v>
       </c>
-      <c r="J41" s="1" t="n">
+      <c r="J41" s="2" t="n">
         <v>43403</v>
       </c>
       <c r="K41" t="n">
@@ -9105,13 +9117,13 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43374</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43465</v>
       </c>
-      <c r="C42" s="1" t="n">
+      <c r="C42" s="2" t="n">
         <v>43522</v>
       </c>
       <c r="D42" t="inlineStr">
@@ -9138,7 +9150,7 @@
       <c r="I42" t="n">
         <v>9.10133843212237</v>
       </c>
-      <c r="J42" s="1" t="n">
+      <c r="J42" s="2" t="n">
         <v>43522</v>
       </c>
       <c r="K42" t="n">
@@ -9151,13 +9163,13 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43466</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43555</v>
       </c>
-      <c r="C43" s="1" t="n">
+      <c r="C43" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="D43" t="inlineStr">
@@ -9184,7 +9196,7 @@
       <c r="I43" t="n">
         <v>9.07265774378585</v>
       </c>
-      <c r="J43" s="1" t="n">
+      <c r="J43" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="K43" t="n">
@@ -9197,13 +9209,13 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43556</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43646</v>
       </c>
-      <c r="C44" s="1" t="n">
+      <c r="C44" s="2" t="n">
         <v>43676</v>
       </c>
       <c r="D44" t="inlineStr">
@@ -9230,7 +9242,7 @@
       <c r="I44" t="n">
         <v>9.263862332695984</v>
       </c>
-      <c r="J44" s="1" t="n">
+      <c r="J44" s="2" t="n">
         <v>43676</v>
       </c>
       <c r="K44" t="n">
@@ -9243,13 +9255,13 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43647</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43738</v>
       </c>
-      <c r="C45" s="1" t="n">
+      <c r="C45" s="2" t="n">
         <v>43768</v>
       </c>
       <c r="D45" t="inlineStr">
@@ -9276,7 +9288,7 @@
       <c r="I45" t="n">
         <v>8.240917782026768</v>
       </c>
-      <c r="J45" s="1" t="n">
+      <c r="J45" s="2" t="n">
         <v>43768</v>
       </c>
       <c r="K45" t="n">
@@ -9289,13 +9301,13 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>43739</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>43830</v>
       </c>
-      <c r="C46" s="1" t="n">
+      <c r="C46" s="2" t="n">
         <v>43886</v>
       </c>
       <c r="D46" t="inlineStr">
@@ -9322,7 +9334,7 @@
       <c r="I46" t="n">
         <v>10.09560229445507</v>
       </c>
-      <c r="J46" s="1" t="n">
+      <c r="J46" s="2" t="n">
         <v>43886</v>
       </c>
       <c r="K46" t="n">
@@ -9335,13 +9347,13 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>43831</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>43921</v>
       </c>
-      <c r="C47" s="1" t="n">
+      <c r="C47" s="2" t="n">
         <v>43949</v>
       </c>
       <c r="D47" t="inlineStr">
@@ -9368,7 +9380,7 @@
       <c r="I47" t="n">
         <v>9.646271510516252</v>
       </c>
-      <c r="J47" s="1" t="n">
+      <c r="J47" s="2" t="n">
         <v>43949</v>
       </c>
       <c r="K47" t="n">
@@ -9381,13 +9393,13 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>43922</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44012</v>
       </c>
-      <c r="C48" s="1" t="n">
+      <c r="C48" s="2" t="n">
         <v>44040</v>
       </c>
       <c r="D48" t="inlineStr">
@@ -9414,7 +9426,7 @@
       <c r="I48" t="n">
         <v>8.413001912045889</v>
       </c>
-      <c r="J48" s="1" t="n">
+      <c r="J48" s="2" t="n">
         <v>44040</v>
       </c>
       <c r="K48" t="n">
@@ -9427,13 +9439,13 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44013</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44104</v>
       </c>
-      <c r="C49" s="1" t="n">
+      <c r="C49" s="2" t="n">
         <v>44131</v>
       </c>
       <c r="D49" t="inlineStr">
@@ -9460,7 +9472,7 @@
       <c r="I49" t="n">
         <v>8.432122370936902</v>
       </c>
-      <c r="J49" s="1" t="n">
+      <c r="J49" s="2" t="n">
         <v>44131</v>
       </c>
       <c r="K49" t="n">
@@ -9473,13 +9485,13 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44105</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44196</v>
       </c>
-      <c r="C50" s="1" t="n">
+      <c r="C50" s="2" t="n">
         <v>44250</v>
       </c>
       <c r="D50" t="inlineStr">
@@ -9506,7 +9518,7 @@
       <c r="I50" t="n">
         <v>5.95602294455067</v>
       </c>
-      <c r="J50" s="1" t="n">
+      <c r="J50" s="2" t="n">
         <v>44250</v>
       </c>
       <c r="K50" t="n">
@@ -9519,13 +9531,13 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44197</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="C51" s="1" t="n">
+      <c r="C51" s="2" t="n">
         <v>44313</v>
       </c>
       <c r="D51" t="inlineStr">
@@ -9552,7 +9564,7 @@
       <c r="I51" t="n">
         <v>5.717017208413003</v>
       </c>
-      <c r="J51" s="1" t="n">
+      <c r="J51" s="2" t="n">
         <v>44313</v>
       </c>
       <c r="K51" t="n">
@@ -9565,13 +9577,13 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44287</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44377</v>
       </c>
-      <c r="C52" s="1" t="n">
+      <c r="C52" s="2" t="n">
         <v>44404</v>
       </c>
       <c r="D52" t="inlineStr">
@@ -9598,7 +9610,7 @@
       <c r="I52" t="n">
         <v>5.669216061185469</v>
       </c>
-      <c r="J52" s="1" t="n">
+      <c r="J52" s="2" t="n">
         <v>44404</v>
       </c>
       <c r="K52" t="n">
@@ -9611,13 +9623,13 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44378</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44469</v>
       </c>
-      <c r="C53" s="1" t="n">
+      <c r="C53" s="2" t="n">
         <v>44505</v>
       </c>
       <c r="D53" t="inlineStr">
@@ -9644,7 +9656,7 @@
       <c r="I53" t="n">
         <v>5.112332695984704</v>
       </c>
-      <c r="J53" s="1" t="n">
+      <c r="J53" s="2" t="n">
         <v>44505</v>
       </c>
       <c r="K53" t="n">
@@ -9657,13 +9669,13 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44470</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44561</v>
       </c>
-      <c r="C54" s="1" t="n">
+      <c r="C54" s="2" t="n">
         <v>44614</v>
       </c>
       <c r="D54" t="inlineStr">
@@ -9690,7 +9702,7 @@
       <c r="I54" t="n">
         <v>6.35</v>
       </c>
-      <c r="J54" s="1" t="n">
+      <c r="J54" s="2" t="n">
         <v>44614</v>
       </c>
       <c r="K54" t="n">
@@ -9703,13 +9715,13 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44562</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44651</v>
       </c>
-      <c r="C55" s="1" t="n">
+      <c r="C55" s="2" t="n">
         <v>44677</v>
       </c>
       <c r="D55" t="inlineStr">
@@ -9736,7 +9748,7 @@
       <c r="I55" t="n">
         <v>6.146615678776291</v>
       </c>
-      <c r="J55" s="1" t="n">
+      <c r="J55" s="2" t="n">
         <v>44677</v>
       </c>
       <c r="K55" t="n">
@@ -9749,13 +9761,13 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44652</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44742</v>
       </c>
-      <c r="C56" s="1" t="n">
+      <c r="C56" s="2" t="n">
         <v>44767</v>
       </c>
       <c r="D56" t="inlineStr">
@@ -9782,7 +9794,7 @@
       <c r="I56" t="n">
         <v>6.271261950286807</v>
       </c>
-      <c r="J56" s="1" t="n">
+      <c r="J56" s="2" t="n">
         <v>44767</v>
       </c>
       <c r="K56" t="n">
@@ -9795,13 +9807,13 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>44743</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>44834</v>
       </c>
-      <c r="C57" s="1" t="n">
+      <c r="C57" s="2" t="n">
         <v>44859</v>
       </c>
       <c r="D57" t="inlineStr">
@@ -9828,7 +9840,7 @@
       <c r="I57" t="n">
         <v>1.481261950286807</v>
       </c>
-      <c r="J57" s="1" t="n">
+      <c r="J57" s="2" t="n">
         <v>44859</v>
       </c>
       <c r="K57" t="n">
@@ -9841,13 +9853,13 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>44835</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>44926</v>
       </c>
-      <c r="C58" s="1" t="n">
+      <c r="C58" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="D58" t="inlineStr">
@@ -9874,7 +9886,7 @@
       <c r="I58" t="n">
         <v>1.8</v>
       </c>
-      <c r="J58" s="1" t="n">
+      <c r="J58" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="K58" t="n">
@@ -9887,13 +9899,13 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>44927</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45016</v>
       </c>
-      <c r="C59" s="1" t="n">
+      <c r="C59" s="2" t="n">
         <v>45041</v>
       </c>
       <c r="D59" t="inlineStr">
@@ -9920,7 +9932,7 @@
       <c r="I59" t="n">
         <v>2</v>
       </c>
-      <c r="J59" s="1" t="n">
+      <c r="J59" s="2" t="n">
         <v>45041</v>
       </c>
       <c r="K59" t="n">
@@ -9933,13 +9945,13 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45017</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="C60" s="1" t="n">
+      <c r="C60" s="2" t="n">
         <v>45132</v>
       </c>
       <c r="D60" t="inlineStr">
@@ -9966,7 +9978,7 @@
       <c r="I60" t="n">
         <v>2.19</v>
       </c>
-      <c r="J60" s="1" t="n">
+      <c r="J60" s="2" t="n">
         <v>45132</v>
       </c>
       <c r="K60" t="n">
@@ -9979,13 +9991,13 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45108</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="C61" s="1" t="n">
+      <c r="C61" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="D61" t="inlineStr">
@@ -10012,7 +10024,7 @@
       <c r="I61" t="n">
         <v>7.57</v>
       </c>
-      <c r="J61" s="1" t="n">
+      <c r="J61" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="K61" t="n">
@@ -10025,13 +10037,13 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45200</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45291</v>
       </c>
-      <c r="C62" s="1" t="n">
+      <c r="C62" s="2" t="n">
         <v>45348</v>
       </c>
       <c r="D62" t="inlineStr">
@@ -10058,7 +10070,7 @@
       <c r="I62" t="n">
         <v>8.140000000000001</v>
       </c>
-      <c r="J62" s="1" t="n">
+      <c r="J62" s="2" t="n">
         <v>45348</v>
       </c>
       <c r="K62" t="n">
@@ -10071,13 +10083,13 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45292</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="C63" s="1" t="n">
+      <c r="C63" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="D63" t="inlineStr">
@@ -10104,7 +10116,7 @@
       <c r="I63" t="n">
         <v>8.85</v>
       </c>
-      <c r="J63" s="1" t="n">
+      <c r="J63" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="K63" t="n">
@@ -10117,13 +10129,13 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45383</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="C64" s="1" t="n">
+      <c r="C64" s="2" t="n">
         <v>45503</v>
       </c>
       <c r="D64" t="inlineStr">
@@ -10150,7 +10162,7 @@
       <c r="I64" t="n">
         <v>9.09</v>
       </c>
-      <c r="J64" s="1" t="n">
+      <c r="J64" s="2" t="n">
         <v>45503</v>
       </c>
       <c r="K64" t="n">
@@ -10163,13 +10175,13 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45474</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="C65" s="1" t="n">
+      <c r="C65" s="2" t="n">
         <v>45595</v>
       </c>
       <c r="D65" t="inlineStr">
@@ -10196,7 +10208,7 @@
       <c r="I65" t="n">
         <v>6.89</v>
       </c>
-      <c r="J65" s="1" t="n">
+      <c r="J65" s="2" t="n">
         <v>45595</v>
       </c>
       <c r="K65" t="n">
@@ -10209,13 +10221,13 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45566</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45657</v>
       </c>
-      <c r="C66" s="1" t="n">
+      <c r="C66" s="2" t="n">
         <v>45713</v>
       </c>
       <c r="D66" t="inlineStr">
@@ -10242,7 +10254,7 @@
       <c r="I66" t="n">
         <v>6.43</v>
       </c>
-      <c r="J66" s="1" t="n">
+      <c r="J66" s="2" t="n">
         <v>45713</v>
       </c>
       <c r="K66" t="n">
@@ -10255,13 +10267,13 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45658</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="C67" s="1" t="n">
+      <c r="C67" s="2" t="n">
         <v>45771</v>
       </c>
       <c r="D67" t="inlineStr">
@@ -10288,7 +10300,7 @@
       <c r="I67" t="n">
         <v>5.83</v>
       </c>
-      <c r="J67" s="1" t="n">
+      <c r="J67" s="2" t="n">
         <v>45771</v>
       </c>
       <c r="K67" t="n">
@@ -10301,13 +10313,13 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>45748</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="C68" s="1" t="n">
+      <c r="C68" s="2" t="n">
         <v>45862</v>
       </c>
       <c r="D68" t="inlineStr">
@@ -10334,7 +10346,7 @@
       <c r="I68" t="n">
         <v>6.18</v>
       </c>
-      <c r="J68" s="1" t="n">
+      <c r="J68" s="2" t="n">
         <v>45862</v>
       </c>
       <c r="K68" t="n">
@@ -10347,13 +10359,13 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>45839</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>45930</v>
       </c>
-      <c r="C69" s="1" t="n">
+      <c r="C69" s="2" t="n">
         <v>45953</v>
       </c>
       <c r="D69" t="inlineStr">
@@ -10380,7 +10392,7 @@
       <c r="I69" t="n">
         <v>8.379999999999999</v>
       </c>
-      <c r="J69" s="1" t="n">
+      <c r="J69" s="2" t="n">
         <v>45953</v>
       </c>
       <c r="K69" t="n">
@@ -10393,13 +10405,13 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>45931</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>46022</v>
       </c>
-      <c r="C70" s="1" t="n">
+      <c r="C70" s="2" t="n">
         <v>46077</v>
       </c>
       <c r="D70" t="inlineStr">
@@ -10426,7 +10438,7 @@
       <c r="I70" t="n">
         <v>11.17</v>
       </c>
-      <c r="J70" s="1" t="n">
+      <c r="J70" s="2" t="n">
         <v>46077</v>
       </c>
       <c r="K70" t="n">
@@ -10439,13 +10451,13 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>46023</v>
       </c>
-      <c r="B71" s="1" t="n">
+      <c r="B71" s="2" t="n">
         <v>46112</v>
       </c>
-      <c r="C71" s="1" t="n">
+      <c r="C71" s="2" t="n">
         <v>46135</v>
       </c>
       <c r="D71" t="inlineStr">
@@ -10472,7 +10484,7 @@
       <c r="I71" t="n">
         <v>11.33</v>
       </c>
-      <c r="J71" s="1" t="n">
+      <c r="J71" s="2" t="n">
         <v>46135</v>
       </c>
       <c r="K71" t="n">
@@ -10485,13 +10497,13 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>46113</v>
       </c>
-      <c r="B72" s="1" t="n">
+      <c r="B72" s="2" t="n">
         <v>46203</v>
       </c>
-      <c r="C72" s="1" t="n">
+      <c r="C72" s="2" t="n">
         <v>46226</v>
       </c>
       <c r="D72" t="inlineStr">
@@ -10518,7 +10530,7 @@
       <c r="I72" t="n">
         <v>11.29</v>
       </c>
-      <c r="J72" s="1" t="n">
+      <c r="J72" s="2" t="n">
         <v>46226</v>
       </c>
       <c r="K72" t="n">
@@ -10555,52 +10567,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>acciones</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39994</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>40022</v>
       </c>
       <c r="C2" t="n">
@@ -10629,10 +10641,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>40086</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>40113</v>
       </c>
       <c r="C3" t="n">
@@ -10661,10 +10673,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>40219</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>40232</v>
       </c>
       <c r="C4" t="n">
@@ -10693,10 +10705,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>40268</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40295</v>
       </c>
       <c r="C5" t="n">
@@ -10725,10 +10737,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40451</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40477</v>
       </c>
       <c r="C6" t="n">
@@ -10757,10 +10769,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40574</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40596</v>
       </c>
       <c r="C7" t="n">
@@ -10789,10 +10801,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40633</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40659</v>
       </c>
       <c r="C8" t="n">
@@ -10821,10 +10833,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40724</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40750</v>
       </c>
       <c r="C9" t="n">
@@ -10853,10 +10865,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40816</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40841</v>
       </c>
       <c r="C10" t="n">
@@ -10885,10 +10897,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40939</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40967</v>
       </c>
       <c r="C11" t="n">
@@ -10917,10 +10929,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40999</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>41023</v>
       </c>
       <c r="C12" t="n">
@@ -10949,10 +10961,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>41090</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>41121</v>
       </c>
       <c r="C13" t="n">
@@ -10981,10 +10993,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>41182</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>41212</v>
       </c>
       <c r="C14" t="n">
@@ -11013,10 +11025,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>41305</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>41331</v>
       </c>
       <c r="C15" t="n">
@@ -11045,10 +11057,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41364</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="C16" t="n">
@@ -11077,10 +11089,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41455</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="C17" t="n">
@@ -11109,10 +11121,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41547</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41576</v>
       </c>
       <c r="C18" t="n">
@@ -11141,10 +11153,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41680</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41695</v>
       </c>
       <c r="C19" t="n">
@@ -11173,10 +11185,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41729</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41758</v>
       </c>
       <c r="C20" t="n">
@@ -11205,10 +11217,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41820</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41849</v>
       </c>
       <c r="C21" t="n">
@@ -11237,10 +11249,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41912</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41940</v>
       </c>
       <c r="C22" t="n">
@@ -11269,10 +11281,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>42045</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>42059</v>
       </c>
       <c r="C23" t="n">
@@ -11301,10 +11313,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>42094</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>42122</v>
       </c>
       <c r="C24" t="n">
@@ -11333,10 +11345,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>42185</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>42213</v>
       </c>
       <c r="C25" t="n">
@@ -11365,10 +11377,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>42277</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42304</v>
       </c>
       <c r="C26" t="n">
@@ -11397,10 +11409,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42410</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42423</v>
       </c>
       <c r="C27" t="n">
@@ -11429,10 +11441,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42460</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42486</v>
       </c>
       <c r="C28" t="n">
@@ -11461,10 +11473,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42551</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42577</v>
       </c>
       <c r="C29" t="n">
@@ -11493,10 +11505,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42643</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42668</v>
       </c>
       <c r="C30" t="n">
@@ -11525,10 +11537,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42776</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="C31" t="n">
@@ -11557,10 +11569,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42825</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42850</v>
       </c>
       <c r="C32" t="n">
@@ -11589,10 +11601,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42916</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42941</v>
       </c>
       <c r="C33" t="n">
@@ -11621,10 +11633,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>43008</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="C34" t="n">
@@ -11653,10 +11665,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>43140</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>43158</v>
       </c>
       <c r="C35" t="n">
@@ -11685,10 +11697,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>43190</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>43214</v>
       </c>
       <c r="C36" t="n">
@@ -11717,10 +11729,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>43281</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="C37" t="n">
@@ -11749,10 +11761,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43373</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43403</v>
       </c>
       <c r="C38" t="n">
@@ -11781,10 +11793,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43504</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43522</v>
       </c>
       <c r="C39" t="n">
@@ -11813,10 +11825,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43555</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="C40" t="n">
@@ -11845,10 +11857,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43646</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43676</v>
       </c>
       <c r="C41" t="n">
@@ -11877,10 +11889,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43738</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43768</v>
       </c>
       <c r="C42" t="n">
@@ -11909,10 +11921,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43871</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43886</v>
       </c>
       <c r="C43" t="n">
@@ -11941,10 +11953,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43921</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43949</v>
       </c>
       <c r="C44" t="n">
@@ -11973,10 +11985,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>44012</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>44040</v>
       </c>
       <c r="C45" t="n">
@@ -12005,10 +12017,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>44104</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>44131</v>
       </c>
       <c r="C46" t="n">
@@ -12037,10 +12049,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>44237</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>44250</v>
       </c>
       <c r="C47" t="n">
@@ -12069,10 +12081,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44313</v>
       </c>
       <c r="C48" t="n">
@@ -12101,10 +12113,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44377</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44404</v>
       </c>
       <c r="C49" t="n">
@@ -12133,10 +12145,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44469</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44505</v>
       </c>
       <c r="C50" t="n">
@@ -12165,10 +12177,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44603</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44614</v>
       </c>
       <c r="C51" t="n">
@@ -12197,10 +12209,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44651</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44677</v>
       </c>
       <c r="C52" t="n">
@@ -12229,10 +12241,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44742</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44767</v>
       </c>
       <c r="C53" t="n">
@@ -12261,10 +12273,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44834</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44859</v>
       </c>
       <c r="C54" t="n">
@@ -12293,10 +12305,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44967</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="C55" t="n">
@@ -12325,10 +12337,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>45016</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>45041</v>
       </c>
       <c r="C56" t="n">
@@ -12357,10 +12369,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>45132</v>
       </c>
       <c r="C57" t="n">
@@ -12389,10 +12401,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="C58" t="n">
@@ -12421,10 +12433,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45331</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45348</v>
       </c>
       <c r="C59" t="n">
@@ -12453,10 +12465,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="C60" t="n">
@@ -12485,10 +12497,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45503</v>
       </c>
       <c r="C61" t="n">
@@ -12517,10 +12529,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45595</v>
       </c>
       <c r="C62" t="n">
@@ -12549,10 +12561,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45698</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45713</v>
       </c>
       <c r="C63" t="n">
@@ -12581,10 +12593,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45771</v>
       </c>
       <c r="C64" t="n">
@@ -12613,10 +12625,10 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45862</v>
       </c>
       <c r="C65" t="n">
@@ -12645,10 +12657,10 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45930</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45953</v>
       </c>
       <c r="C66" t="n">
@@ -12677,10 +12689,10 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>46063</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>46077</v>
       </c>
       <c r="C67" t="n">
@@ -12709,10 +12721,10 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>46112</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>46135</v>
       </c>
       <c r="C68" t="n">
@@ -12741,10 +12753,10 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>46203</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>46226</v>
       </c>
       <c r="C69" t="n">
@@ -12791,12 +12803,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>

--- a/salidas/empresas/IBM.xlsx
+++ b/salidas/empresas/IBM.xlsx
@@ -498,7 +498,7 @@
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>41.10723495483398</v>
+        <v>41.10723114013672</v>
       </c>
       <c r="C2" t="n">
         <v>77.72466278076172</v>
@@ -517,7 +517,7 @@
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>40.67315673828125</v>
+        <v>40.67314910888672</v>
       </c>
       <c r="C3" t="n">
         <v>76.71128082275391</v>
@@ -536,7 +536,7 @@
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>41.80353927612305</v>
+        <v>41.80353164672852</v>
       </c>
       <c r="C4" t="n">
         <v>78.84320831298828</v>
@@ -555,7 +555,7 @@
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>41.73764038085938</v>
+        <v>41.73761749267578</v>
       </c>
       <c r="C5" t="n">
         <v>78.71892547607422</v>
@@ -574,7 +574,7 @@
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>40.6472282409668</v>
+        <v>40.64725112915039</v>
       </c>
       <c r="C6" t="n">
         <v>76.38623046875</v>
@@ -650,7 +650,7 @@
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>41.85131454467773</v>
+        <v>41.85131072998047</v>
       </c>
       <c r="C10" t="n">
         <v>78.33651733398438</v>
@@ -669,7 +669,7 @@
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>47.15805053710938</v>
+        <v>47.15804672241211</v>
       </c>
       <c r="C11" t="n">
         <v>88.26959991455078</v>
@@ -688,7 +688,7 @@
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>47.10099029541016</v>
+        <v>47.10098648071289</v>
       </c>
       <c r="C12" t="n">
         <v>87.87763214111328</v>
@@ -707,7 +707,7 @@
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>49.78089904785156</v>
+        <v>49.7808952331543</v>
       </c>
       <c r="C13" t="n">
         <v>92.87763214111328</v>
@@ -726,7 +726,7 @@
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>50.80572509765625</v>
+        <v>50.80571746826172</v>
       </c>
       <c r="C14" t="n">
         <v>94.7896728515625</v>
@@ -745,7 +745,7 @@
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>47.76717376708984</v>
+        <v>47.76715850830078</v>
       </c>
       <c r="C15" t="n">
         <v>88.85277557373047</v>
@@ -764,7 +764,7 @@
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>48.44557571411133</v>
+        <v>48.44558334350586</v>
       </c>
       <c r="C16" t="n">
         <v>90.11472320556641</v>
@@ -783,7 +783,7 @@
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>52.53155136108398</v>
+        <v>52.53155899047852</v>
       </c>
       <c r="C17" t="n">
         <v>97.71510314941406</v>
@@ -802,7 +802,7 @@
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>55.00107192993164</v>
+        <v>55.00107574462891</v>
       </c>
       <c r="C18" t="n">
         <v>101.9120483398438</v>
@@ -821,7 +821,7 @@
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>54.30453872680664</v>
+        <v>54.30450820922852</v>
       </c>
       <c r="C19" t="n">
         <v>100.6214141845703</v>
@@ -840,7 +840,7 @@
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>57.09068298339844</v>
+        <v>57.09069442749023</v>
       </c>
       <c r="C20" t="n">
         <v>105.783935546875</v>
@@ -859,7 +859,7 @@
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>60.41997528076172</v>
+        <v>60.41994094848633</v>
       </c>
       <c r="C21" t="n">
         <v>111.5583190917969</v>
@@ -878,7 +878,7 @@
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>60.99469757080078</v>
+        <v>60.99467849731445</v>
       </c>
       <c r="C22" t="n">
         <v>112.619499206543</v>
@@ -897,7 +897,7 @@
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>60.12482452392578</v>
+        <v>60.12485885620117</v>
       </c>
       <c r="C23" t="n">
         <v>111.0133819580078</v>
@@ -916,7 +916,7 @@
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>54.65345764160156</v>
+        <v>54.65348052978516</v>
       </c>
       <c r="C24" t="n">
         <v>100.5544967651367</v>
@@ -935,7 +935,7 @@
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>56.17075729370117</v>
+        <v>56.17072677612305</v>
       </c>
       <c r="C25" t="n">
         <v>103.346076965332</v>
@@ -954,7 +954,7 @@
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>55.65634155273438</v>
+        <v>55.65632629394531</v>
       </c>
       <c r="C26" t="n">
         <v>102.3996200561523</v>
@@ -992,7 +992,7 @@
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>60.05760955810547</v>
+        <v>60.05760192871094</v>
       </c>
       <c r="C28" t="n">
         <v>110.0764846801758</v>
@@ -1011,7 +1011,7 @@
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>62.9577522277832</v>
+        <v>62.95774841308594</v>
       </c>
       <c r="C29" t="n">
         <v>115.3919677734375</v>
@@ -1030,7 +1030,7 @@
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>67.78733062744141</v>
+        <v>67.78728485107422</v>
       </c>
       <c r="C30" t="n">
         <v>123.7380523681641</v>
@@ -1049,7 +1049,7 @@
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>62.07857513427734</v>
+        <v>62.07855224609375</v>
       </c>
       <c r="C31" t="n">
         <v>113.3173980712891</v>
@@ -1068,7 +1068,7 @@
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>67.02790069580078</v>
+        <v>67.02790832519531</v>
       </c>
       <c r="C32" t="n">
         <v>122.3518142700195</v>
@@ -1087,7 +1087,7 @@
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>64.00283813476562</v>
+        <v>64.00285339355469</v>
       </c>
       <c r="C33" t="n">
         <v>116.3766708374023</v>
@@ -1106,7 +1106,7 @@
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>61.49491119384766</v>
+        <v>61.49490737915039</v>
       </c>
       <c r="C34" t="n">
         <v>111.8164443969727</v>
@@ -1125,7 +1125,7 @@
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>48.88150405883789</v>
+        <v>48.88148880004883</v>
       </c>
       <c r="C35" t="n">
         <v>88.88145446777344</v>
@@ -1144,7 +1144,7 @@
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>43.14326858520508</v>
+        <v>43.14326095581055</v>
       </c>
       <c r="C36" t="n">
         <v>78.011474609375</v>
@@ -1163,7 +1163,7 @@
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>44.49678039550781</v>
+        <v>44.49676513671875</v>
       </c>
       <c r="C37" t="n">
         <v>80.45889282226562</v>
@@ -1182,7 +1182,7 @@
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>48.45686340332031</v>
+        <v>48.45684814453125</v>
       </c>
       <c r="C38" t="n">
         <v>87.61949920654297</v>
@@ -1201,7 +1201,7 @@
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>48.9224739074707</v>
+        <v>48.92248153686523</v>
       </c>
       <c r="C39" t="n">
         <v>87.98279571533203</v>
@@ -1220,7 +1220,7 @@
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>51.50602340698242</v>
+        <v>51.50600814819336</v>
       </c>
       <c r="C40" t="n">
         <v>92.62906646728516</v>
@@ -1239,7 +1239,7 @@
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>54.86566925048828</v>
+        <v>54.86568832397461</v>
       </c>
       <c r="C41" t="n">
         <v>98.67112731933594</v>
@@ -1277,7 +1277,7 @@
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>55.79884719848633</v>
+        <v>55.79887008666992</v>
       </c>
       <c r="C43" t="n">
         <v>99.82791900634766</v>
@@ -1296,7 +1296,7 @@
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>63.01816558837891</v>
+        <v>63.01819610595703</v>
       </c>
       <c r="C44" t="n">
         <v>112.7437896728516</v>
@@ -1346,7 +1346,7 @@
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>64.21404266357422</v>
+        <v>64.21402740478516</v>
       </c>
       <c r="C46" t="n">
         <v>114.3499069213867</v>
@@ -1396,7 +1396,7 @@
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>68.13691711425781</v>
+        <v>68.13693237304688</v>
       </c>
       <c r="C48" t="n">
         <v>120.7935028076172</v>
@@ -1421,7 +1421,7 @@
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>70.590576171875</v>
+        <v>70.59059143066406</v>
       </c>
       <c r="C49" t="n">
         <v>125.1434020996094</v>
@@ -1446,7 +1446,7 @@
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>66.00138854980469</v>
+        <v>66.00140380859375</v>
       </c>
       <c r="C50" t="n">
         <v>117.0076446533203</v>
@@ -1471,7 +1471,7 @@
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>68.88040924072266</v>
+        <v>68.88043212890625</v>
       </c>
       <c r="C51" t="n">
         <v>121.5678787231445</v>
@@ -1496,7 +1496,7 @@
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>69.47088623046875</v>
+        <v>69.47084808349609</v>
       </c>
       <c r="C52" t="n">
         <v>122.6099395751953</v>
@@ -1521,7 +1521,7 @@
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>69.87711334228516</v>
+        <v>69.87713623046875</v>
       </c>
       <c r="C53" t="n">
         <v>123.3269577026367</v>
@@ -1546,7 +1546,7 @@
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>68.19902038574219</v>
+        <v>68.19900512695312</v>
       </c>
       <c r="C54" t="n">
         <v>119.7514343261719</v>
@@ -1571,7 +1571,7 @@
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>67.22988128662109</v>
+        <v>67.2298583984375</v>
       </c>
       <c r="C55" t="n">
         <v>118.0497131347656</v>
@@ -1621,7 +1621,7 @@
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>67.37150573730469</v>
+        <v>67.37151336669922</v>
       </c>
       <c r="C57" t="n">
         <v>117.7151031494141</v>
@@ -1646,7 +1646,7 @@
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>73.39569854736328</v>
+        <v>73.39571380615234</v>
       </c>
       <c r="C58" t="n">
         <v>128.2409210205078</v>
@@ -1671,7 +1671,7 @@
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>78.57185363769531</v>
+        <v>78.57183837890625</v>
       </c>
       <c r="C59" t="n">
         <v>137.2848968505859</v>
@@ -1696,7 +1696,7 @@
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>77.74483489990234</v>
+        <v>77.74484252929688</v>
       </c>
       <c r="C60" t="n">
         <v>135.2389984130859</v>
@@ -1721,7 +1721,7 @@
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>80.65767669677734</v>
+        <v>80.65769195556641</v>
       </c>
       <c r="C61" t="n">
         <v>140.3059234619141</v>
@@ -1800,7 +1800,7 @@
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>89.976318359375</v>
+        <v>89.97630310058594</v>
       </c>
       <c r="C64" t="n">
         <v>155.8986663818359</v>
@@ -1829,7 +1829,7 @@
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>94.12007904052734</v>
+        <v>94.12004089355469</v>
       </c>
       <c r="C65" t="n">
         <v>163.0783996582031</v>
@@ -1858,7 +1858,7 @@
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>93.62647247314453</v>
+        <v>93.62645721435547</v>
       </c>
       <c r="C66" t="n">
         <v>161.5009613037109</v>
@@ -1887,7 +1887,7 @@
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>95.07856750488281</v>
+        <v>95.07859039306641</v>
       </c>
       <c r="C67" t="n">
         <v>164.0057373046875</v>
@@ -1916,7 +1916,7 @@
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>100.7871475219727</v>
+        <v>100.7871627807617</v>
       </c>
       <c r="C68" t="n">
         <v>173.8527679443359</v>
@@ -1945,7 +1945,7 @@
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>95.69303894042969</v>
+        <v>95.69300079345703</v>
       </c>
       <c r="C69" t="n">
         <v>164.3498992919922</v>
@@ -1974,7 +1974,7 @@
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>97.34065246582031</v>
+        <v>97.34064483642578</v>
       </c>
       <c r="C70" t="n">
         <v>167.1797332763672</v>
@@ -2003,7 +2003,7 @@
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>102.7735595703125</v>
+        <v>102.7735290527344</v>
       </c>
       <c r="C71" t="n">
         <v>176.5105133056641</v>
@@ -2032,7 +2032,7 @@
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>105.0701293945312</v>
+        <v>105.0701599121094</v>
       </c>
       <c r="C72" t="n">
         <v>179.7323150634766</v>
@@ -2061,7 +2061,7 @@
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>102.767578125</v>
+        <v>102.7674789428711</v>
       </c>
       <c r="C73" t="n">
         <v>175.7935028076172</v>
@@ -2090,7 +2090,7 @@
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>107.640983581543</v>
+        <v>107.6409759521484</v>
       </c>
       <c r="C74" t="n">
         <v>184.1300201416016</v>
@@ -2119,7 +2119,7 @@
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>110.3773193359375</v>
+        <v>110.3773651123047</v>
       </c>
       <c r="C75" t="n">
         <v>188.0783996582031</v>
@@ -2148,7 +2148,7 @@
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>117.0651321411133</v>
+        <v>117.0651473999023</v>
       </c>
       <c r="C76" t="n">
         <v>199.4741821289062</v>
@@ -2177,7 +2177,7 @@
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>116.184326171875</v>
+        <v>116.1842803955078</v>
       </c>
       <c r="C77" t="n">
         <v>197.9732360839844</v>
@@ -2206,7 +2206,7 @@
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>108.6818771362305</v>
+        <v>108.6818542480469</v>
       </c>
       <c r="C78" t="n">
         <v>184.4168243408203</v>
@@ -2235,7 +2235,7 @@
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>110.1918334960938</v>
+        <v>110.191780090332</v>
       </c>
       <c r="C79" t="n">
         <v>186.9789733886719</v>
@@ -2264,7 +2264,7 @@
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>110.4171676635742</v>
+        <v>110.4171905517578</v>
       </c>
       <c r="C80" t="n">
         <v>187.3613739013672</v>
@@ -2293,7 +2293,7 @@
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>110.2491760253906</v>
+        <v>110.249267578125</v>
       </c>
       <c r="C81" t="n">
         <v>186.2810668945312</v>
@@ -2322,7 +2322,7 @@
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>117.3784866333008</v>
+        <v>117.3785400390625</v>
       </c>
       <c r="C82" t="n">
         <v>198.3269653320312</v>
@@ -2351,7 +2351,7 @@
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>110.0681533813477</v>
+        <v>110.0681838989258</v>
       </c>
       <c r="C83" t="n">
         <v>185.9751434326172</v>
@@ -2380,7 +2380,7 @@
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>108.0153045654297</v>
+        <v>108.0152893066406</v>
       </c>
       <c r="C84" t="n">
         <v>181.7112884521484</v>
@@ -2409,7 +2409,7 @@
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>108.8563232421875</v>
+        <v>108.8563766479492</v>
       </c>
       <c r="C85" t="n">
         <v>183.1261901855469</v>
@@ -2438,7 +2438,7 @@
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>115.403076171875</v>
+        <v>115.4030609130859</v>
       </c>
       <c r="C86" t="n">
         <v>194.1395721435547</v>
@@ -2467,7 +2467,7 @@
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>114.6105499267578</v>
+        <v>114.6105117797852</v>
       </c>
       <c r="C87" t="n">
         <v>191.9980926513672</v>
@@ -2496,7 +2496,7 @@
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>121.7269515991211</v>
+        <v>121.7269439697266</v>
       </c>
       <c r="C88" t="n">
         <v>203.9196929931641</v>
@@ -2525,7 +2525,7 @@
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>115.5863723754883</v>
+        <v>115.5864181518555</v>
       </c>
       <c r="C89" t="n">
         <v>193.6328887939453</v>
@@ -2554,7 +2554,7 @@
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>119.2701797485352</v>
+        <v>119.270133972168</v>
       </c>
       <c r="C90" t="n">
         <v>198.8718872070312</v>
@@ -2583,7 +2583,7 @@
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>109.5746459960938</v>
+        <v>109.5746841430664</v>
       </c>
       <c r="C91" t="n">
         <v>182.7055511474609</v>
@@ -2612,7 +2612,7 @@
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>111.8279800415039</v>
+        <v>111.8279037475586</v>
       </c>
       <c r="C92" t="n">
         <v>186.4627075195312</v>
@@ -2641,7 +2641,7 @@
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>105.0285720825195</v>
+        <v>105.0285797119141</v>
       </c>
       <c r="C93" t="n">
         <v>174.2543029785156</v>
@@ -2670,7 +2670,7 @@
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>106.7053985595703</v>
+        <v>106.7054138183594</v>
       </c>
       <c r="C94" t="n">
         <v>177.0363311767578</v>
@@ -2699,7 +2699,7 @@
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>103.2653503417969</v>
+        <v>103.2653350830078</v>
       </c>
       <c r="C95" t="n">
         <v>171.3288726806641</v>
@@ -2757,7 +2757,7 @@
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>108.6630172729492</v>
+        <v>108.6630020141602</v>
       </c>
       <c r="C97" t="n">
         <v>179.3212280273438</v>
@@ -2786,7 +2786,7 @@
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>102.3542404174805</v>
+        <v>102.3541717529297</v>
       </c>
       <c r="C98" t="n">
         <v>168.9101409912109</v>
@@ -2815,7 +2815,7 @@
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>107.8607635498047</v>
+        <v>107.860725402832</v>
       </c>
       <c r="C99" t="n">
         <v>177.0267639160156</v>
@@ -2844,7 +2844,7 @@
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>112.1246566772461</v>
+        <v>112.1246032714844</v>
       </c>
       <c r="C100" t="n">
         <v>184.0248565673828</v>
@@ -2873,7 +2873,7 @@
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>114.4429550170898</v>
+        <v>114.4429016113281</v>
       </c>
       <c r="C101" t="n">
         <v>187.829833984375</v>
@@ -2902,7 +2902,7 @@
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>108.01416015625</v>
+        <v>108.0141525268555</v>
       </c>
       <c r="C102" t="n">
         <v>176.2523956298828</v>
@@ -2931,7 +2931,7 @@
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>106.2037506103516</v>
+        <v>106.2037811279297</v>
       </c>
       <c r="C103" t="n">
         <v>173.2982788085938</v>
@@ -2960,7 +2960,7 @@
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>112.2969818115234</v>
+        <v>112.2969741821289</v>
       </c>
       <c r="C104" t="n">
         <v>183.2409210205078</v>
@@ -2989,7 +2989,7 @@
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>113.3323974609375</v>
+        <v>113.3324279785156</v>
       </c>
       <c r="C105" t="n">
         <v>183.8432159423828</v>
@@ -3018,7 +3018,7 @@
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>111.8766860961914</v>
+        <v>111.8767318725586</v>
       </c>
       <c r="C106" t="n">
         <v>181.4818420410156</v>
@@ -3047,7 +3047,7 @@
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>96.88950347900391</v>
+        <v>96.88945770263672</v>
       </c>
       <c r="C107" t="n">
         <v>157.170166015625</v>
@@ -3076,7 +3076,7 @@
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>96.22937774658203</v>
+        <v>96.22933959960938</v>
       </c>
       <c r="C108" t="n">
         <v>155.0382385253906</v>
@@ -3105,7 +3105,7 @@
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>95.20281219482422</v>
+        <v>95.20278930664062</v>
       </c>
       <c r="C109" t="n">
         <v>153.3843231201172</v>
@@ -3134,7 +3134,7 @@
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>90.97196197509766</v>
+        <v>90.97196960449219</v>
       </c>
       <c r="C110" t="n">
         <v>146.56787109375</v>
@@ -3163,7 +3163,7 @@
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>96.76696014404297</v>
+        <v>96.76699066162109</v>
       </c>
       <c r="C111" t="n">
         <v>154.818359375</v>
@@ -3221,7 +3221,7 @@
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>102.3540573120117</v>
+        <v>102.3540496826172</v>
       </c>
       <c r="C113" t="n">
         <v>163.7571716308594</v>
@@ -3279,7 +3279,7 @@
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>97.93276977539062</v>
+        <v>97.93279266357422</v>
       </c>
       <c r="C115" t="n">
         <v>155.5066986083984</v>
@@ -3308,7 +3308,7 @@
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>97.52938842773438</v>
+        <v>97.52939605712891</v>
       </c>
       <c r="C116" t="n">
         <v>154.8661499023438</v>
@@ -3337,7 +3337,7 @@
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>89.77934265136719</v>
+        <v>89.77935791015625</v>
       </c>
       <c r="C117" t="n">
         <v>141.38623046875</v>
@@ -3395,7 +3395,7 @@
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>85.03812408447266</v>
+        <v>85.03816223144531</v>
       </c>
       <c r="C119" t="n">
         <v>133.9196929931641</v>
@@ -3424,7 +3424,7 @@
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>85.431396484375</v>
+        <v>85.43137359619141</v>
       </c>
       <c r="C120" t="n">
         <v>133.2887115478516</v>
@@ -3453,7 +3453,7 @@
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>84.32840728759766</v>
+        <v>84.32839965820312</v>
       </c>
       <c r="C121" t="n">
         <v>131.56787109375</v>
@@ -3482,7 +3482,7 @@
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>76.46665191650391</v>
+        <v>76.46666717529297</v>
       </c>
       <c r="C122" t="n">
         <v>119.3021011352539</v>
@@ -3540,7 +3540,7 @@
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>93.7508544921875</v>
+        <v>93.75088500976562</v>
       </c>
       <c r="C124" t="n">
         <v>144.7896728515625</v>
@@ -3598,7 +3598,7 @@
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>96.08682250976562</v>
+        <v>96.08683013916016</v>
       </c>
       <c r="C126" t="n">
         <v>146.9789733886719</v>
@@ -3627,7 +3627,7 @@
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>94.86184692382812</v>
+        <v>94.86187744140625</v>
       </c>
       <c r="C127" t="n">
         <v>145.1051635742188</v>
@@ -3714,7 +3714,7 @@
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>100.1380386352539</v>
+        <v>100.1380081176758</v>
       </c>
       <c r="C130" t="n">
         <v>151.8642425537109</v>
@@ -3743,7 +3743,7 @@
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>96.88520812988281</v>
+        <v>96.88519287109375</v>
       </c>
       <c r="C131" t="n">
         <v>146.9311676025391</v>
@@ -3772,7 +3772,7 @@
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>103.1901702880859</v>
+        <v>103.1901626586914</v>
       </c>
       <c r="C132" t="n">
         <v>155.0860443115234</v>
@@ -3801,7 +3801,7 @@
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>105.5883255004883</v>
+        <v>105.5883331298828</v>
       </c>
       <c r="C133" t="n">
         <v>158.6902465820312</v>
@@ -3830,7 +3830,7 @@
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>111.0143966674805</v>
+        <v>111.0143585205078</v>
       </c>
       <c r="C134" t="n">
         <v>166.8451232910156</v>
@@ -3859,7 +3859,7 @@
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>115.2902145385742</v>
+        <v>115.2902297973633</v>
       </c>
       <c r="C135" t="n">
         <v>171.9120483398438</v>
@@ -3888,7 +3888,7 @@
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>111.6485137939453</v>
+        <v>111.6484985351562</v>
       </c>
       <c r="C136" t="n">
         <v>166.4818420410156</v>
@@ -3917,7 +3917,7 @@
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>102.768669128418</v>
+        <v>102.7687072753906</v>
       </c>
       <c r="C137" t="n">
         <v>153.2409210205078</v>
@@ -3946,7 +3946,7 @@
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>98.81350708007812</v>
+        <v>98.81352233886719</v>
       </c>
       <c r="C138" t="n">
         <v>145.9177856445312</v>
@@ -3975,7 +3975,7 @@
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>99.59038543701172</v>
+        <v>99.59036254882812</v>
       </c>
       <c r="C139" t="n">
         <v>147.0650024414062</v>
@@ -4004,7 +4004,7 @@
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>93.66015625</v>
+        <v>93.66016387939453</v>
       </c>
       <c r="C140" t="n">
         <v>138.3078460693359</v>
@@ -4033,7 +4033,7 @@
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>93.57677459716797</v>
+        <v>93.57674407958984</v>
       </c>
       <c r="C141" t="n">
         <v>136.7399597167969</v>
@@ -4062,7 +4062,7 @@
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>94.91797637939453</v>
+        <v>94.91798400878906</v>
       </c>
       <c r="C142" t="n">
         <v>138.6998138427734</v>
@@ -4091,7 +4091,7 @@
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>100.7930679321289</v>
+        <v>100.7930908203125</v>
       </c>
       <c r="C143" t="n">
         <v>147.2848968505859</v>
@@ -4120,7 +4120,7 @@
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>101.7410736083984</v>
+        <v>101.7410888671875</v>
       </c>
       <c r="C144" t="n">
         <v>147.1988525390625</v>
@@ -4149,7 +4149,7 @@
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>101.3776473999023</v>
+        <v>101.3776931762695</v>
       </c>
       <c r="C145" t="n">
         <v>146.6730346679688</v>
@@ -4178,7 +4178,7 @@
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>108.170539855957</v>
+        <v>108.1704940795898</v>
       </c>
       <c r="C146" t="n">
         <v>156.5009613037109</v>
@@ -4236,7 +4236,7 @@
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>102.3824691772461</v>
+        <v>102.3824462890625</v>
       </c>
       <c r="C148" t="n">
         <v>146.6826019287109</v>
@@ -4265,7 +4265,7 @@
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>96.73050689697266</v>
+        <v>96.73051452636719</v>
       </c>
       <c r="C149" t="n">
         <v>138.5850830078125</v>
@@ -4294,7 +4294,7 @@
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>95.34165954589844</v>
+        <v>95.34162902832031</v>
       </c>
       <c r="C150" t="n">
         <v>135.0955963134766</v>
@@ -4323,7 +4323,7 @@
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>94.25539398193359</v>
+        <v>94.25537872314453</v>
       </c>
       <c r="C151" t="n">
         <v>133.5564117431641</v>
@@ -4352,7 +4352,7 @@
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>97.78408050537109</v>
+        <v>97.78404235839844</v>
       </c>
       <c r="C152" t="n">
         <v>138.5564117431641</v>
@@ -4381,7 +4381,7 @@
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>99.89759063720703</v>
+        <v>99.89756011962891</v>
       </c>
       <c r="C153" t="n">
         <v>140.0382385253906</v>
@@ -4410,7 +4410,7 @@
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>103.1233901977539</v>
+        <v>103.1233520507812</v>
       </c>
       <c r="C154" t="n">
         <v>144.5602264404297</v>
@@ -4439,7 +4439,7 @@
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>78.72184753417969</v>
+        <v>78.72186279296875</v>
       </c>
       <c r="C155" t="n">
         <v>110.3537292480469</v>
@@ -4497,7 +4497,7 @@
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>78.50887298583984</v>
+        <v>78.50888061523438</v>
       </c>
       <c r="C157" t="n">
         <v>108.6711273193359</v>
@@ -4526,7 +4526,7 @@
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>92.84037017822266</v>
+        <v>92.84036254882812</v>
       </c>
       <c r="C158" t="n">
         <v>128.5086059570312</v>
@@ -4613,7 +4613,7 @@
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>98.00959014892578</v>
+        <v>98.00960540771484</v>
       </c>
       <c r="C161" t="n">
         <v>134.1013336181641</v>
@@ -4671,7 +4671,7 @@
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>97.49818420410156</v>
+        <v>97.49817657470703</v>
       </c>
       <c r="C163" t="n">
         <v>131.8355712890625</v>
@@ -4700,7 +4700,7 @@
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>104.8087692260742</v>
+        <v>104.8087463378906</v>
       </c>
       <c r="C164" t="n">
         <v>141.7208404541016</v>
@@ -4729,7 +4729,7 @@
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>96.95157623291016</v>
+        <v>96.95156860351562</v>
       </c>
       <c r="C165" t="n">
         <v>129.5697937011719</v>
@@ -4758,7 +4758,7 @@
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>104.0263977050781</v>
+        <v>104.0264053344727</v>
       </c>
       <c r="C166" t="n">
         <v>139.0248565673828</v>
@@ -4816,7 +4816,7 @@
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>97.31497955322266</v>
+        <v>97.31498718261719</v>
       </c>
       <c r="C168" t="n">
         <v>128.5372924804688</v>
@@ -4845,7 +4845,7 @@
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>97.01820373535156</v>
+        <v>97.01821136474609</v>
       </c>
       <c r="C169" t="n">
         <v>128.1453094482422</v>
@@ -4874,7 +4874,7 @@
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>104.0318450927734</v>
+        <v>104.0318145751953</v>
       </c>
       <c r="C170" t="n">
         <v>137.4091796875</v>
@@ -4903,7 +4903,7 @@
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>95.18630218505859</v>
+        <v>95.18630981445312</v>
       </c>
       <c r="C171" t="n">
         <v>124.426383972168</v>
@@ -4932,7 +4932,7 @@
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>81.12960052490234</v>
+        <v>81.12959289550781</v>
       </c>
       <c r="C172" t="n">
         <v>106.051628112793</v>
@@ -4961,7 +4961,7 @@
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>91.82938385009766</v>
+        <v>91.82936096191406</v>
       </c>
       <c r="C173" t="n">
         <v>120.0382385253906</v>
@@ -4990,7 +4990,7 @@
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>92.57172393798828</v>
+        <v>92.57173919677734</v>
       </c>
       <c r="C174" t="n">
         <v>119.4072647094727</v>
@@ -5077,7 +5077,7 @@
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>92.58992004394531</v>
+        <v>92.58993530273438</v>
       </c>
       <c r="C177" t="n">
         <v>117.8871917724609</v>
@@ -5106,7 +5106,7 @@
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>91.3585205078125</v>
+        <v>91.35848999023438</v>
       </c>
       <c r="C178" t="n">
         <v>116.3193130493164</v>
@@ -5135,7 +5135,7 @@
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>83.84229278564453</v>
+        <v>83.84227752685547</v>
       </c>
       <c r="C179" t="n">
         <v>106.7495193481445</v>
@@ -5164,7 +5164,7 @@
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>94.09249877929688</v>
+        <v>94.09250640869141</v>
       </c>
       <c r="C180" t="n">
         <v>118.0879516601562</v>
@@ -5222,7 +5222,7 @@
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>90.73314666748047</v>
+        <v>90.73313903808594</v>
       </c>
       <c r="C182" t="n">
         <v>113.8718948364258</v>
@@ -5251,7 +5251,7 @@
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>91.806640625</v>
+        <v>91.80666351318359</v>
       </c>
       <c r="C183" t="n">
         <v>113.6998062133789</v>
@@ -5280,7 +5280,7 @@
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>102.8685531616211</v>
+        <v>102.8685150146484</v>
       </c>
       <c r="C184" t="n">
         <v>127.3996200561523</v>
@@ -5309,7 +5309,7 @@
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>109.5226516723633</v>
+        <v>109.5226440429688</v>
       </c>
       <c r="C185" t="n">
         <v>135.6405334472656</v>
@@ -5338,7 +5338,7 @@
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>112.1981964111328</v>
+        <v>112.1982040405273</v>
       </c>
       <c r="C186" t="n">
         <v>137.4187316894531</v>
@@ -5367,7 +5367,7 @@
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>114.4228210449219</v>
+        <v>114.4227981567383</v>
       </c>
       <c r="C187" t="n">
         <v>140.1434020996094</v>
@@ -5396,7 +5396,7 @@
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>110.0282440185547</v>
+        <v>110.0282287597656</v>
       </c>
       <c r="C188" t="n">
         <v>134.7610015869141</v>
@@ -5425,7 +5425,7 @@
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>110.8054733276367</v>
+        <v>110.8054504394531</v>
       </c>
       <c r="C189" t="n">
         <v>134.1682586669922</v>
@@ -5483,7 +5483,7 @@
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>98.77271270751953</v>
+        <v>98.77272033691406</v>
       </c>
       <c r="C191" t="n">
         <v>119.5984725952148</v>
@@ -5512,7 +5512,7 @@
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>97.99980163574219</v>
+        <v>97.99980926513672</v>
       </c>
       <c r="C192" t="n">
         <v>117.0999984741211</v>
@@ -5541,7 +5541,7 @@
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>111.8587036132812</v>
+        <v>111.8587265014648</v>
       </c>
       <c r="C193" t="n">
         <v>133.6600036621094</v>
@@ -5570,7 +5570,7 @@
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>111.7834091186523</v>
+        <v>111.7833709716797</v>
       </c>
       <c r="C194" t="n">
         <v>133.5700073242188</v>
@@ -5628,7 +5628,7 @@
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>110.1231384277344</v>
+        <v>110.1231231689453</v>
       </c>
       <c r="C196" t="n">
         <v>130.0200042724609</v>
@@ -5657,7 +5657,7 @@
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>111.97802734375</v>
+        <v>111.9780197143555</v>
       </c>
       <c r="C197" t="n">
         <v>132.2100067138672</v>
@@ -5686,7 +5686,7 @@
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>119.0198974609375</v>
+        <v>119.0198593139648</v>
       </c>
       <c r="C198" t="n">
         <v>138.8399963378906</v>
@@ -5715,7 +5715,7 @@
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>121.034423828125</v>
+        <v>121.0344161987305</v>
       </c>
       <c r="C199" t="n">
         <v>141.1900024414062</v>
@@ -5802,7 +5802,7 @@
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>103.1324996948242</v>
+        <v>103.1325073242188</v>
       </c>
       <c r="C202" t="n">
         <v>118.8099975585938</v>
@@ -5831,7 +5831,7 @@
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>120.0420227050781</v>
+        <v>120.0420150756836</v>
       </c>
       <c r="C203" t="n">
         <v>138.2899932861328</v>
@@ -5860,7 +5860,7 @@
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>130.7930603027344</v>
+        <v>130.7930450439453</v>
       </c>
       <c r="C204" t="n">
         <v>148.8999938964844</v>
@@ -5889,7 +5889,7 @@
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>123.7571029663086</v>
+        <v>123.7570724487305</v>
       </c>
       <c r="C205" t="n">
         <v>140.8899993896484</v>
@@ -5918,7 +5918,7 @@
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>118.3461761474609</v>
+        <v>118.3461837768555</v>
       </c>
       <c r="C206" t="n">
         <v>134.7299957275391</v>
@@ -5947,7 +5947,7 @@
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>114.9715805053711</v>
+        <v>114.9715728759766</v>
       </c>
       <c r="C207" t="n">
         <v>129.3000030517578</v>
@@ -6005,7 +6005,7 @@
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>112.4018325805664</v>
+        <v>112.4018249511719</v>
       </c>
       <c r="C209" t="n">
         <v>126.4100036621094</v>
@@ -6063,7 +6063,7 @@
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>120.6041946411133</v>
+        <v>120.6041641235352</v>
       </c>
       <c r="C211" t="n">
         <v>133.8099975585938</v>
@@ -6092,7 +6092,7 @@
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>129.9507598876953</v>
+        <v>129.9507446289062</v>
       </c>
       <c r="C212" t="n">
         <v>144.1799926757812</v>
@@ -6121,7 +6121,7 @@
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>133.8621673583984</v>
+        <v>133.8621368408203</v>
       </c>
       <c r="C213" t="n">
         <v>146.8300018310547</v>
@@ -6150,7 +6150,7 @@
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>127.9088668823242</v>
+        <v>127.9088973999023</v>
       </c>
       <c r="C214" t="n">
         <v>140.3000030517578</v>
@@ -6295,7 +6295,7 @@
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>172.1568756103516</v>
+        <v>172.1568603515625</v>
       </c>
       <c r="C219" t="n">
         <v>185.0299987792969</v>
@@ -6324,7 +6324,7 @@
         <v>45382</v>
       </c>
       <c r="B220" t="n">
-        <v>177.6742858886719</v>
+        <v>177.67431640625</v>
       </c>
       <c r="C220" t="n">
         <v>190.9600067138672</v>
@@ -6353,7 +6353,7 @@
         <v>45412</v>
       </c>
       <c r="B221" t="n">
-        <v>154.6369018554688</v>
+        <v>154.6369323730469</v>
       </c>
       <c r="C221" t="n">
         <v>166.1999969482422</v>
@@ -6440,7 +6440,7 @@
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>180.5468139648438</v>
+        <v>180.5468292236328</v>
       </c>
       <c r="C224" t="n">
         <v>192.1399993896484</v>
@@ -6498,7 +6498,7 @@
         <v>45565</v>
       </c>
       <c r="B226" t="n">
-        <v>209.5576324462891</v>
+        <v>209.5576477050781</v>
       </c>
       <c r="C226" t="n">
         <v>221.0800018310547</v>
@@ -6556,7 +6556,7 @@
         <v>45626</v>
       </c>
       <c r="B228" t="n">
-        <v>217.2565612792969</v>
+        <v>217.2565765380859</v>
       </c>
       <c r="C228" t="n">
         <v>227.4100036621094</v>
@@ -6585,7 +6585,7 @@
         <v>45657</v>
       </c>
       <c r="B229" t="n">
-        <v>210.0149841308594</v>
+        <v>210.0149993896484</v>
       </c>
       <c r="C229" t="n">
         <v>219.8300018310547</v>
@@ -6614,7 +6614,7 @@
         <v>45688</v>
       </c>
       <c r="B230" t="n">
-        <v>244.283447265625</v>
+        <v>244.2834625244141</v>
       </c>
       <c r="C230" t="n">
         <v>255.6999969482422</v>
@@ -6643,7 +6643,7 @@
         <v>45716</v>
       </c>
       <c r="B231" t="n">
-        <v>242.7757415771484</v>
+        <v>242.7757263183594</v>
       </c>
       <c r="C231" t="n">
         <v>252.4400024414062</v>
@@ -6672,7 +6672,7 @@
         <v>45747</v>
       </c>
       <c r="B232" t="n">
-        <v>239.1404418945312</v>
+        <v>239.1404266357422</v>
       </c>
       <c r="C232" t="n">
         <v>248.6600036621094</v>
@@ -6701,7 +6701,7 @@
         <v>45777</v>
       </c>
       <c r="B233" t="n">
-        <v>232.5623168945312</v>
+        <v>232.5623016357422</v>
       </c>
       <c r="C233" t="n">
         <v>241.8200073242188</v>
@@ -6759,7 +6759,7 @@
         <v>45838</v>
       </c>
       <c r="B235" t="n">
-        <v>285.38134765625</v>
+        <v>285.3813171386719</v>
       </c>
       <c r="C235" t="n">
         <v>294.7799987792969</v>
@@ -6788,7 +6788,7 @@
         <v>45869</v>
       </c>
       <c r="B236" t="n">
-        <v>245.0786437988281</v>
+        <v>245.0786285400391</v>
       </c>
       <c r="C236" t="n">
         <v>253.1499938964844</v>
@@ -6933,7 +6933,7 @@
         <v>46022</v>
       </c>
       <c r="B241" t="n">
-        <v>290.29638671875</v>
+        <v>290.2964172363281</v>
       </c>
       <c r="C241" t="n">
         <v>296.2099914550781</v>
@@ -6991,7 +6991,7 @@
         <v>46081</v>
       </c>
       <c r="B243" t="n">
-        <v>236.7566223144531</v>
+        <v>236.7566070556641</v>
       </c>
       <c r="C243" t="n">
         <v>240.2100067138672</v>
@@ -7049,7 +7049,7 @@
         <v>46142</v>
       </c>
       <c r="B245" t="n">
-        <v>227.6592864990234</v>
+        <v>227.6593017578125</v>
       </c>
       <c r="C245" t="n">
         <v>230.9799957275391</v>
